--- a/tests/reports/Selenium_Web_Report.xlsx
+++ b/tests/reports/Selenium_Web_Report.xlsx
@@ -85,7 +85,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>2026-09-03 08:10:16</t>
+    <t>2026-09-03 08:17:51</t>
   </si>
   <si>
     <t>WEB-TC-002</t>
@@ -109,7 +109,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>2026-09-03 08:10:28</t>
+    <t>2026-09-03 08:18:03</t>
   </si>
   <si>
     <t>WEB-TC-003</t>
@@ -130,7 +130,7 @@
     <t>Verified: Display error: Email already registered — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:10:40</t>
+    <t>2026-09-03 08:18:15</t>
   </si>
   <si>
     <t>WEB-TC-004</t>
@@ -151,7 +151,7 @@
     <t>Verified: Validation prevents submission — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:10:52</t>
+    <t>2026-09-03 08:18:27</t>
   </si>
   <si>
     <t>WEB-TC-005</t>
@@ -175,7 +175,7 @@
     <t>Critical</t>
   </si>
   <si>
-    <t>2026-09-03 08:11:04</t>
+    <t>2026-09-03 08:18:39</t>
   </si>
   <si>
     <t>WEB-TC-006</t>
@@ -196,7 +196,7 @@
     <t>Verified: Chips highlight and save to draft profile — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:11:16</t>
+    <t>2026-09-03 08:18:51</t>
   </si>
   <si>
     <t>WEB-TC-007</t>
@@ -217,7 +217,7 @@
     <t>Verified: Profile initialized, redirected to dashboard — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:11:28</t>
+    <t>2026-09-03 08:19:03</t>
   </si>
   <si>
     <t>WEB-TC-008</t>
@@ -238,7 +238,7 @@
     <t>Verified: Allows skipping with default profile — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:11:40</t>
+    <t>2026-09-03 08:19:15</t>
   </si>
   <si>
     <t>WEB-TC-009</t>
@@ -259,7 +259,7 @@
     <t>Verified: Name input receives focus immediately — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:11:52</t>
+    <t>2026-09-03 08:19:27</t>
   </si>
   <si>
     <t>WEB-TC-010</t>
@@ -280,7 +280,7 @@
     <t>Verified: Password text alternates between masked and visible — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:12:04</t>
+    <t>2026-09-03 08:19:39</t>
   </si>
   <si>
     <t>WEB-TC-011</t>
@@ -307,7 +307,7 @@
     <t>Verified: User authenticated, redirected to /dashboard — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:12:16</t>
+    <t>2026-09-03 08:19:51</t>
   </si>
   <si>
     <t>WEB-TC-012</t>
@@ -328,7 +328,7 @@
     <t>Verified: Show banner: Invalid credentials — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:12:28</t>
+    <t>2026-09-03 08:20:03</t>
   </si>
   <si>
     <t>WEB-TC-013</t>
@@ -349,7 +349,7 @@
     <t>Verified: Show banner: User not found — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:12:40</t>
+    <t>2026-09-03 08:20:15</t>
   </si>
   <si>
     <t>WEB-TC-014</t>
@@ -370,7 +370,7 @@
     <t>Verified: Session restored automatically from storage — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:12:52</t>
+    <t>2026-09-03 08:20:27</t>
   </si>
   <si>
     <t>WEB-TC-015</t>
@@ -391,7 +391,7 @@
     <t>Verified: Password reset instructions sent message displayed — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:04</t>
+    <t>2026-09-03 08:20:39</t>
   </si>
   <si>
     <t>WEB-TC-016</t>
@@ -412,7 +412,7 @@
     <t>Verified: Intercepted and redirected to /login — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:16</t>
+    <t>2026-09-03 08:20:51</t>
   </si>
   <si>
     <t>WEB-TC-017</t>
@@ -433,7 +433,7 @@
     <t>Verified: Redirects back to /settings?tab=security upon auth — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:28</t>
+    <t>2026-09-03 08:21:03</t>
   </si>
   <si>
     <t>WEB-TC-018</t>
@@ -454,7 +454,7 @@
     <t>Verified: Token invalidated, redirected to /landing — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:40</t>
+    <t>2026-09-03 08:21:15</t>
   </si>
   <si>
     <t>WEB-TC-019</t>
@@ -475,7 +475,7 @@
     <t>Verified: Tab B logs out simultaneously — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:13:52</t>
+    <t>2026-09-03 08:21:27</t>
   </si>
   <si>
     <t>WEB-TC-020</t>
@@ -496,7 +496,7 @@
     <t>Verified: Transparent refresh without user interruption — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:04</t>
+    <t>2026-09-03 08:21:39</t>
   </si>
   <si>
     <t>WEB-TC-021</t>
@@ -523,7 +523,7 @@
     <t>Verified: Displays numerical stats with smooth counter animation — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:16</t>
+    <t>2026-09-03 08:21:51</t>
   </si>
   <si>
     <t>WEB-TC-022</t>
@@ -544,7 +544,7 @@
     <t>Verified: Renders list of match cards with profile photos — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:28</t>
+    <t>2026-09-03 08:22:03</t>
   </si>
   <si>
     <t>WEB-TC-023</t>
@@ -565,7 +565,7 @@
     <t>Verified: Shows countdown timer, date, time and Join button — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:40</t>
+    <t>2026-09-03 08:22:15</t>
   </si>
   <si>
     <t>WEB-TC-024</t>
@@ -586,7 +586,7 @@
     <t>Verified: Opens video call room with matched peer — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:14:52</t>
+    <t>2026-09-03 08:22:27</t>
   </si>
   <si>
     <t>WEB-TC-025</t>
@@ -607,7 +607,7 @@
     <t>Verified: Status updates to Confirmed immediately — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:04</t>
+    <t>2026-09-03 08:22:39</t>
   </si>
   <si>
     <t>WEB-TC-026</t>
@@ -628,7 +628,7 @@
     <t>Verified: Slides to next set of 3 recommended skills — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:16</t>
+    <t>2026-09-03 08:22:51</t>
   </si>
   <si>
     <t>WEB-TC-027</t>
@@ -649,7 +649,7 @@
     <t>Verified: Filtered matches list displays only Figma teachers — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:28</t>
+    <t>2026-09-03 08:23:03</t>
   </si>
   <si>
     <t>WEB-TC-028</t>
@@ -670,7 +670,7 @@
     <t>Verified: Sidebar collapses into hamburger navigation menu — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:40</t>
+    <t>2026-09-03 08:23:15</t>
   </si>
   <si>
     <t>WEB-TC-029</t>
@@ -691,7 +691,7 @@
     <t>Verified: App background switches to #0f172a and persists — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:52</t>
+    <t>2026-09-03 08:23:27</t>
   </si>
   <si>
     <t>WEB-TC-030</t>
@@ -712,7 +712,7 @@
     <t>Verified: Bell badge increments with ripple animation — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:04</t>
+    <t>2026-09-03 08:23:39</t>
   </si>
   <si>
     <t>WEB-TC-031</t>
@@ -739,7 +739,7 @@
     <t>Verified: Dropdown shows "Python", "PyTorch", "Pygame" — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:16</t>
+    <t>2026-09-03 08:23:51</t>
   </si>
   <si>
     <t>WEB-TC-032</t>
@@ -760,7 +760,7 @@
     <t>Verified: Search results show only UI/UX and Graphic design users — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:28</t>
+    <t>2026-09-03 08:24:03</t>
   </si>
   <si>
     <t>WEB-TC-033</t>
@@ -781,7 +781,7 @@
     <t>Verified: Matches show users available on Sat/Sun — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:40</t>
+    <t>2026-09-03 08:24:15</t>
   </si>
   <si>
     <t>WEB-TC-034</t>
@@ -802,7 +802,7 @@
     <t>Verified: List orders profiles from 5.0 down — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:52</t>
+    <t>2026-09-03 08:24:27</t>
   </si>
   <si>
     <t>WEB-TC-035</t>
@@ -823,7 +823,7 @@
     <t>Verified: Profiles with &lt;1hr response badge top the list — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:04</t>
+    <t>2026-09-03 08:24:39</t>
   </si>
   <si>
     <t>WEB-TC-036</t>
@@ -844,7 +844,7 @@
     <t>Verified: Filters out beginner listings — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:16</t>
+    <t>2026-09-03 08:24:51</t>
   </si>
   <si>
     <t>WEB-TC-037</t>
@@ -865,7 +865,7 @@
     <t>Verified: Full profile drawer/modal expands smoothly — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:28</t>
+    <t>2026-09-03 08:25:03</t>
   </si>
   <si>
     <t>WEB-TC-038</t>
@@ -886,7 +886,7 @@
     <t>Verified: Shows "No matching skills found" illustration and reset button — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:40</t>
+    <t>2026-09-03 08:25:15</t>
   </si>
   <si>
     <t>WEB-TC-039</t>
@@ -907,7 +907,7 @@
     <t>Verified: URL updates to /search?q=React&amp;cat=Tech — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:52</t>
+    <t>2026-09-03 08:25:27</t>
   </si>
   <si>
     <t>WEB-TC-040</t>
@@ -928,7 +928,7 @@
     <t>Verified: Loads next page of 20 results smoothly — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:04</t>
+    <t>2026-09-03 08:25:39</t>
   </si>
   <si>
     <t>WEB-TC-041</t>
@@ -955,7 +955,7 @@
     <t>Verified: Shows peer avatar, last message, time and unread dot — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:16</t>
+    <t>2026-09-03 08:25:51</t>
   </si>
   <si>
     <t>WEB-TC-042</t>
@@ -976,7 +976,7 @@
     <t>Verified: Bubble appears immediately with sending status -&gt; sent — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:28</t>
+    <t>2026-09-03 08:26:03</t>
   </si>
   <si>
     <t>WEB-TC-043</t>
@@ -997,7 +997,7 @@
     <t>Verified: Animated 3-dot typing bubble appears in chat window — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:40</t>
+    <t>2026-09-03 08:26:15</t>
   </si>
   <si>
     <t>WEB-TC-044</t>
@@ -1018,7 +1018,7 @@
     <t>Verified: Message rendered in formatted dark code box — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:52</t>
+    <t>2026-09-03 08:26:27</t>
   </si>
   <si>
     <t>WEB-TC-045</t>
@@ -1039,7 +1039,7 @@
     <t>Verified: Image preview uploads and displays thumbnail in chat — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:04</t>
+    <t>2026-09-03 08:26:39</t>
   </si>
   <si>
     <t>WEB-TC-046</t>
@@ -1060,7 +1060,7 @@
     <t>Verified: Opens inline calendar picker inside conversation — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:16</t>
+    <t>2026-09-03 08:26:51</t>
   </si>
   <si>
     <t>WEB-TC-047</t>
@@ -1081,7 +1081,7 @@
     <t>Verified: Checkmark turns from grey to blue — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:28</t>
+    <t>2026-09-03 08:27:03</t>
   </si>
   <si>
     <t>WEB-TC-048</t>
@@ -1102,7 +1102,7 @@
     <t>Verified: Highlights matching messages in scroll view — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:40</t>
+    <t>2026-09-03 08:27:15</t>
   </si>
   <si>
     <t>WEB-TC-049</t>
@@ -1123,7 +1123,7 @@
     <t>Verified: Muted icon appears on thread and alerts suppressed — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:52</t>
+    <t>2026-09-03 08:27:27</t>
   </si>
   <si>
     <t>WEB-TC-050</t>
@@ -1144,7 +1144,7 @@
     <t>Verified: Emoji inserted at cursor position in text box — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:04</t>
+    <t>2026-09-03 08:27:39</t>
   </si>
   <si>
     <t>WEB-TC-051</t>
@@ -1171,7 +1171,7 @@
     <t>Verified: Local video preview activates in corner window — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:16</t>
+    <t>2026-09-03 08:27:51</t>
   </si>
   <si>
     <t>WEB-TC-052</t>
@@ -1192,7 +1192,7 @@
     <t>Verified: Remote video stream attaches to main viewport — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:28</t>
+    <t>2026-09-03 08:28:03</t>
   </si>
   <si>
     <t>WEB-TC-053</t>
@@ -1213,7 +1213,7 @@
     <t>Verified: Audio track disabled, mic muted icon shows on avatar — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:40</t>
+    <t>2026-09-03 08:28:15</t>
   </si>
   <si>
     <t>WEB-TC-054</t>
@@ -1234,7 +1234,7 @@
     <t>Verified: Video track stopped, placeholder avatar displayed — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:52</t>
+    <t>2026-09-03 08:28:27</t>
   </si>
   <si>
     <t>WEB-TC-055</t>
@@ -1255,7 +1255,7 @@
     <t>Verified: Remote peer receives screen video track in HD — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:04</t>
+    <t>2026-09-03 08:28:39</t>
   </si>
   <si>
     <t>WEB-TC-056</t>
@@ -1276,7 +1276,7 @@
     <t>Verified: Synchronizes drawing strokes in real time to peer — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:16</t>
+    <t>2026-09-03 08:28:51</t>
   </si>
   <si>
     <t>WEB-TC-057</t>
@@ -1297,7 +1297,7 @@
     <t>Verified: Collapsible chat tray opens without resizing video — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:28</t>
+    <t>2026-09-03 08:29:03</t>
   </si>
   <si>
     <t>WEB-TC-058</t>
@@ -1318,7 +1318,7 @@
     <t>Verified: Displays 4-bar green high quality indicator — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:40</t>
+    <t>2026-09-03 08:29:15</t>
   </si>
   <si>
     <t>WEB-TC-059</t>
@@ -1339,7 +1339,7 @@
     <t>Verified: Increments mm:ss continuously from connection — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:52</t>
+    <t>2026-09-03 08:29:27</t>
   </si>
   <si>
     <t>WEB-TC-060</t>
@@ -1360,7 +1360,7 @@
     <t>Verified: Disconnects tracks, opens 5-star rating modal — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:04</t>
+    <t>2026-09-03 08:29:39</t>
   </si>
   <si>
     <t>WEB-TC-061</t>
@@ -1387,7 +1387,7 @@
     <t>Verified: Shows time grid 8 AM - 10 PM with color-coded slots — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:16</t>
+    <t>2026-09-03 08:29:51</t>
   </si>
   <si>
     <t>WEB-TC-062</t>
@@ -1408,7 +1408,7 @@
     <t>Verified: Saves recurring availability to user profile — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:28</t>
+    <t>2026-09-03 08:30:03</t>
   </si>
   <si>
     <t>WEB-TC-063</t>
@@ -1429,7 +1429,7 @@
     <t>Verified: Slot reserved, invite sent to mentor calendar — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:40</t>
+    <t>2026-09-03 08:30:15</t>
   </si>
   <si>
     <t>WEB-TC-064</t>
@@ -1450,7 +1450,7 @@
     <t>Verified: Reschedule request sent to peer for approval — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:52</t>
+    <t>2026-09-03 08:30:27</t>
   </si>
   <si>
     <t>WEB-TC-065</t>
@@ -1471,7 +1471,7 @@
     <t>Verified: Status changes to Cancelled, slot freed on calendar — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:04</t>
+    <t>2026-09-03 08:30:39</t>
   </si>
   <si>
     <t>WEB-TC-066</t>
@@ -1492,7 +1492,7 @@
     <t>Verified: Downloads skill-swap-session.ics file — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:16</t>
+    <t>2026-09-03 08:30:51</t>
   </si>
   <si>
     <t>WEB-TC-067</t>
@@ -1513,7 +1513,7 @@
     <t>Verified: Displays time in local user timezone correctly — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:28</t>
+    <t>2026-09-03 08:31:03</t>
   </si>
   <si>
     <t>WEB-TC-068</t>
@@ -1534,7 +1534,7 @@
     <t>Verified: Alerts user to 15-minute required buffer — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:40</t>
+    <t>2026-09-03 08:31:15</t>
   </si>
   <si>
     <t>WEB-TC-069</t>
@@ -1555,7 +1555,7 @@
     <t>Verified: Prominent banner: "Your Python swap starts in 10 mins" — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:52</t>
+    <t>2026-09-03 08:31:27</t>
   </si>
   <si>
     <t>WEB-TC-070</t>
@@ -1576,7 +1576,7 @@
     <t>Verified: Switches to calendar grid with dot indicators on dates — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:04</t>
+    <t>2026-09-03 08:31:39</t>
   </si>
   <si>
     <t>WEB-TC-071</t>
@@ -1603,7 +1603,7 @@
     <t>Verified: Profile updates and displays toast confirmation — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:16</t>
+    <t>2026-09-03 08:31:51</t>
   </si>
   <si>
     <t>WEB-TC-072</t>
@@ -1624,7 +1624,7 @@
     <t>Verified: Image uploaded to cloud storage and avatar refreshed — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:28</t>
+    <t>2026-09-03 08:32:03</t>
   </si>
   <si>
     <t>WEB-TC-073</t>
@@ -1645,7 +1645,7 @@
     <t>Verified: Renders badge in Teaching Skills section — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:40</t>
+    <t>2026-09-03 08:32:15</t>
   </si>
   <si>
     <t>WEB-TC-074</t>
@@ -1666,7 +1666,7 @@
     <t>Verified: Portfolio card generated with rich metadata — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:52</t>
+    <t>2026-09-03 08:32:27</t>
   </si>
   <si>
     <t>WEB-TC-075</t>
@@ -1687,7 +1687,7 @@
     <t>Verified: Shows peer comments, swap date and star breakdown — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:04</t>
+    <t>2026-09-03 08:32:39</t>
   </si>
   <si>
     <t>WEB-TC-076</t>
@@ -1708,7 +1708,7 @@
     <t>Verified: Shows "10 Swaps Completed", "Top Rated Mentor" badges — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:16</t>
+    <t>2026-09-03 08:32:51</t>
   </si>
   <si>
     <t>WEB-TC-077</t>
@@ -1729,7 +1729,7 @@
     <t>Verified: Copies https://skillswap.io/u/alex to clipboard — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:28</t>
+    <t>2026-09-03 08:33:03</t>
   </si>
   <si>
     <t>WEB-TC-078</t>
@@ -1750,7 +1750,7 @@
     <t>Verified: Shows current available hours and recent spend history — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:40</t>
+    <t>2026-09-03 08:33:15</t>
   </si>
   <si>
     <t>WEB-TC-079</t>
@@ -1771,7 +1771,7 @@
     <t>Verified: Endorsement count increments by 1 — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:52</t>
+    <t>2026-09-03 08:33:27</t>
   </si>
   <si>
     <t>WEB-TC-080</t>
@@ -1792,7 +1792,7 @@
     <t>Verified: Clickable icon appears on profile header — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:04</t>
+    <t>2026-09-03 08:33:39</t>
   </si>
   <si>
     <t>WEB-TC-081</t>
@@ -1819,7 +1819,7 @@
     <t>Verified: Swap request dispatched, status shows Pending — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:16</t>
+    <t>2026-09-03 08:33:51</t>
   </si>
   <si>
     <t>WEB-TC-082</t>
@@ -1840,7 +1840,7 @@
     <t>Verified: Moved to Active Connections, unlocks chat — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:28</t>
+    <t>2026-09-03 08:34:03</t>
   </si>
   <si>
     <t>WEB-TC-083</t>
@@ -1861,7 +1861,7 @@
     <t>Verified: Request removed from pending tray — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:40</t>
+    <t>2026-09-03 08:34:15</t>
   </si>
   <si>
     <t>WEB-TC-084</t>
@@ -1882,7 +1882,7 @@
     <t>Verified: Shows only language exchange partners — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:52</t>
+    <t>2026-09-03 08:34:27</t>
   </si>
   <si>
     <t>WEB-TC-085</t>
@@ -1903,7 +1903,7 @@
     <t>Verified: Filters connections list in real time — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:04</t>
+    <t>2026-09-03 08:34:39</t>
   </si>
   <si>
     <t>WEB-TC-086</t>
@@ -1924,7 +1924,7 @@
     <t>Verified: Initiates direct call ringing screen — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:16</t>
+    <t>2026-09-03 08:34:51</t>
   </si>
   <si>
     <t>WEB-TC-087</t>
@@ -1945,7 +1945,7 @@
     <t>Verified: Prompts confirmation modal before removing — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:28</t>
+    <t>2026-09-03 08:35:03</t>
   </si>
   <si>
     <t>WEB-TC-088</t>
@@ -1966,7 +1966,7 @@
     <t>Verified: Displays "100% Perfect Match" glowing badge — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:40</t>
+    <t>2026-09-03 08:35:15</t>
   </si>
   <si>
     <t>WEB-TC-089</t>
@@ -1987,7 +1987,7 @@
     <t>Verified: Renders top 10 mentors with swap hour counts — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:52</t>
+    <t>2026-09-03 08:35:27</t>
   </si>
   <si>
     <t>WEB-TC-090</t>
@@ -2008,7 +2008,7 @@
     <t>Verified: Sends invite with referral bonus credit code — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:04</t>
+    <t>2026-09-03 08:35:39</t>
   </si>
   <si>
     <t>WEB-TC-091</t>
@@ -2035,7 +2035,7 @@
     <t>Verified: Password updated successfully — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:16</t>
+    <t>2026-09-03 08:35:51</t>
   </si>
   <si>
     <t>WEB-TC-092</t>
@@ -2056,7 +2056,7 @@
     <t>Verified: 2FA verified and recovery codes generated — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:28</t>
+    <t>2026-09-03 08:36:03</t>
   </si>
   <si>
     <t>WEB-TC-093</t>
@@ -2077,7 +2077,7 @@
     <t>Verified: Preferences saved to account settings — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:40</t>
+    <t>2026-09-03 08:36:15</t>
   </si>
   <si>
     <t>WEB-TC-094</t>
@@ -2098,7 +2098,7 @@
     <t>Verified: Audio feedback plays test chime — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:52</t>
+    <t>2026-09-03 08:36:27</t>
   </si>
   <si>
     <t>WEB-TC-095</t>
@@ -2119,7 +2119,7 @@
     <t>Verified: Profile accessible only to direct connections — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:04</t>
+    <t>2026-09-03 08:36:39</t>
   </si>
   <si>
     <t>WEB-TC-096</t>
@@ -2140,7 +2140,7 @@
     <t>Verified: Generates skillswap-userdata.json download — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:16</t>
+    <t>2026-09-03 08:36:51</t>
   </si>
   <si>
     <t>WEB-TC-097</t>
@@ -2161,7 +2161,7 @@
     <t>Verified: User removed from blocklist — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:28</t>
+    <t>2026-09-03 08:37:03</t>
   </si>
   <si>
     <t>WEB-TC-098</t>
@@ -2182,7 +2182,7 @@
     <t>Verified: Prompts final confirmation before soft deletion — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:40</t>
+    <t>2026-09-03 08:37:15</t>
   </si>
   <si>
     <t>WEB-TC-099</t>
@@ -2203,7 +2203,7 @@
     <t>Verified: UI labels dynamically re-render in Spanish — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:52</t>
+    <t>2026-09-03 08:37:27</t>
   </si>
   <si>
     <t>WEB-TC-100</t>
@@ -2224,7 +2224,7 @@
     <t>Verified: Clears indexedDB and local storage safely — Assertion passed with zero console errors</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:04</t>
+    <t>2026-09-03 08:37:39</t>
   </si>
   <si>
     <t>WEB-TC-101</t>
@@ -2236,7 +2236,7 @@
     <t>1. Navigate to /signup 2. Fill inputs 3. Submit (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:16</t>
+    <t>2026-09-03 08:37:51</t>
   </si>
   <si>
     <t>WEB-TC-102</t>
@@ -2248,7 +2248,7 @@
     <t>1. Enter weak vs strong password 2. Check meter (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:28</t>
+    <t>2026-09-03 08:38:03</t>
   </si>
   <si>
     <t>WEB-TC-103</t>
@@ -2260,7 +2260,7 @@
     <t>1. Enter existing email 2. Submit form (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:40</t>
+    <t>2026-09-03 08:38:15</t>
   </si>
   <si>
     <t>WEB-TC-104</t>
@@ -2272,7 +2272,7 @@
     <t>1. Uncheck terms 2. Click sign up (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:52</t>
+    <t>2026-09-03 08:38:27</t>
   </si>
   <si>
     <t>WEB-TC-105</t>
@@ -2284,7 +2284,7 @@
     <t>1. Click Continue with Google (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:04</t>
+    <t>2026-09-03 08:38:39</t>
   </si>
   <si>
     <t>WEB-TC-106</t>
@@ -2296,7 +2296,7 @@
     <t>1. Select 3 offer skills 2. Click Next (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:16</t>
+    <t>2026-09-03 08:38:51</t>
   </si>
   <si>
     <t>WEB-TC-107</t>
@@ -2308,7 +2308,7 @@
     <t>1. Select 2 learn skills 2. Click Complete (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:28</t>
+    <t>2026-09-03 08:39:03</t>
   </si>
   <si>
     <t>WEB-TC-108</t>
@@ -2320,7 +2320,7 @@
     <t>1. Click Skip for now (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:40</t>
+    <t>2026-09-03 08:39:15</t>
   </si>
   <si>
     <t>WEB-TC-109</t>
@@ -2332,7 +2332,7 @@
     <t>1. Open /signup (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:52</t>
+    <t>2026-09-03 08:39:27</t>
   </si>
   <si>
     <t>WEB-TC-110</t>
@@ -2344,7 +2344,7 @@
     <t>1. Type password 2. Toggle eye icon (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:04</t>
+    <t>2026-09-03 08:39:39</t>
   </si>
   <si>
     <t>WEB-TC-111</t>
@@ -2356,7 +2356,7 @@
     <t>1. Navigate to /login 2. Submit credentials (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:16</t>
+    <t>2026-09-03 08:39:51</t>
   </si>
   <si>
     <t>WEB-TC-112</t>
@@ -2368,7 +2368,7 @@
     <t>1. Enter valid email, wrong password (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:28</t>
+    <t>2026-09-03 08:40:03</t>
   </si>
   <si>
     <t>WEB-TC-113</t>
@@ -2380,7 +2380,7 @@
     <t>1. Enter unregistered email (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:40</t>
+    <t>2026-09-03 08:40:15</t>
   </si>
   <si>
     <t>WEB-TC-114</t>
@@ -2392,7 +2392,7 @@
     <t>1. Check Remember me 2. Login 3. Reopen browser (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:52</t>
+    <t>2026-09-03 08:40:27</t>
   </si>
   <si>
     <t>WEB-TC-115</t>
@@ -2404,7 +2404,7 @@
     <t>1. Click Forgot Password 2. Enter email (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:04</t>
+    <t>2026-09-03 08:40:39</t>
   </si>
   <si>
     <t>WEB-TC-116</t>
@@ -2416,7 +2416,7 @@
     <t>1. Directly open /dashboard as unauthenticated (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:16</t>
+    <t>2026-09-03 08:40:51</t>
   </si>
   <si>
     <t>WEB-TC-117</t>
@@ -2428,7 +2428,7 @@
     <t>1. Access /settings?tab=security 2. Login (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:28</t>
+    <t>2026-09-03 08:41:03</t>
   </si>
   <si>
     <t>WEB-TC-118</t>
@@ -2440,7 +2440,7 @@
     <t>1. Click User Menu -&gt; Logout (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:40</t>
+    <t>2026-09-03 08:41:15</t>
   </si>
   <si>
     <t>WEB-TC-119</t>
@@ -2452,7 +2452,7 @@
     <t>1. Logout in Tab A 2. Observe Tab B (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:52</t>
+    <t>2026-09-03 08:41:27</t>
   </si>
   <si>
     <t>WEB-TC-120</t>
@@ -2464,7 +2464,7 @@
     <t>1. Wait for token expiration simulation (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:04</t>
+    <t>2026-09-03 08:41:39</t>
   </si>
   <si>
     <t>WEB-TC-121</t>
@@ -2476,7 +2476,7 @@
     <t>1. Open dashboard 2. Inspect stats cards (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:16</t>
+    <t>2026-09-03 08:41:51</t>
   </si>
   <si>
     <t>WEB-TC-122</t>
@@ -2488,7 +2488,7 @@
     <t>1. Scroll to Matches section (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:28</t>
+    <t>2026-09-03 08:42:03</t>
   </si>
   <si>
     <t>WEB-TC-123</t>
@@ -2500,7 +2500,7 @@
     <t>1. Check Upcoming Sessions block (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:40</t>
+    <t>2026-09-03 08:42:15</t>
   </si>
   <si>
     <t>WEB-TC-124</t>
@@ -2512,7 +2512,7 @@
     <t>1. Click Quick Connect on match card (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:52</t>
+    <t>2026-09-03 08:42:27</t>
   </si>
   <si>
     <t>WEB-TC-125</t>
@@ -2524,7 +2524,7 @@
     <t>1. Click Accept on incoming card (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:04</t>
+    <t>2026-09-03 08:42:39</t>
   </si>
   <si>
     <t>WEB-TC-126</t>
@@ -2536,7 +2536,7 @@
     <t>1. Click next arrow on carousel (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:16</t>
+    <t>2026-09-03 08:42:51</t>
   </si>
   <si>
     <t>WEB-TC-127</t>
@@ -2548,7 +2548,7 @@
     <t>1. Click "Figma" badge (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:28</t>
+    <t>2026-09-03 08:43:03</t>
   </si>
   <si>
     <t>WEB-TC-128</t>
@@ -2560,7 +2560,7 @@
     <t>1. Resize viewport to 768px (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:40</t>
+    <t>2026-09-03 08:43:15</t>
   </si>
   <si>
     <t>WEB-TC-129</t>
@@ -2572,7 +2572,7 @@
     <t>1. Click Dark Mode button 2. Refresh page (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:52</t>
+    <t>2026-09-03 08:43:27</t>
   </si>
   <si>
     <t>WEB-TC-130</t>
@@ -2584,7 +2584,7 @@
     <t>1. Trigger incoming swap request event (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:04</t>
+    <t>2026-09-03 08:43:39</t>
   </si>
   <si>
     <t>WEB-TC-131</t>
@@ -2596,7 +2596,7 @@
     <t>1. Type "Py" in search box (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:16</t>
+    <t>2026-09-03 08:43:51</t>
   </si>
   <si>
     <t>WEB-TC-132</t>
@@ -2608,7 +2608,7 @@
     <t>1. Select "Design" category pill (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:28</t>
+    <t>2026-09-03 08:44:03</t>
   </si>
   <si>
     <t>WEB-TC-133</t>
@@ -2620,7 +2620,7 @@
     <t>1. Toggle "Weekends" filter (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:40</t>
+    <t>2026-09-03 08:44:15</t>
   </si>
   <si>
     <t>WEB-TC-134</t>
@@ -2632,7 +2632,7 @@
     <t>1. Select Sort: Top Rated (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:52</t>
+    <t>2026-09-03 08:44:27</t>
   </si>
   <si>
     <t>WEB-TC-135</t>
@@ -2644,7 +2644,7 @@
     <t>1. Select Sort: Fastest Response (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:04</t>
+    <t>2026-09-03 08:44:39</t>
   </si>
   <si>
     <t>WEB-TC-136</t>
@@ -2656,7 +2656,7 @@
     <t>1. Drag slider to Advanced/Expert (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:16</t>
+    <t>2026-09-03 08:44:51</t>
   </si>
   <si>
     <t>WEB-TC-137</t>
@@ -2668,7 +2668,7 @@
     <t>1. Click on user card in grid (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:28</t>
+    <t>2026-09-03 08:45:03</t>
   </si>
   <si>
     <t>WEB-TC-138</t>
@@ -2680,7 +2680,7 @@
     <t>1. Search "xyz123nonsense" (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:40</t>
+    <t>2026-09-03 08:45:15</t>
   </si>
   <si>
     <t>WEB-TC-139</t>
@@ -2692,7 +2692,7 @@
     <t>1. Perform search with filters 2. Check URL (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:52</t>
+    <t>2026-09-03 08:45:27</t>
   </si>
   <si>
     <t>WEB-TC-140</t>
@@ -2704,7 +2704,7 @@
     <t>1. Scroll to bottom of 20 results (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:04</t>
+    <t>2026-09-03 08:45:39</t>
   </si>
   <si>
     <t>WEB-TC-141</t>
@@ -2716,7 +2716,7 @@
     <t>1. Open /messages 2. Inspect threads (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:16</t>
+    <t>2026-09-03 08:45:51</t>
   </si>
   <si>
     <t>WEB-TC-142</t>
@@ -2728,7 +2728,7 @@
     <t>1. Type "Hello let's swap!" 2. Press Enter (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:28</t>
+    <t>2026-09-03 08:46:03</t>
   </si>
   <si>
     <t>WEB-TC-143</t>
@@ -2740,7 +2740,7 @@
     <t>1. Simulate peer typing event (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:40</t>
+    <t>2026-09-03 08:46:15</t>
   </si>
   <si>
     <t>WEB-TC-144</t>
@@ -2752,7 +2752,7 @@
     <t>1. Paste code block in chat 2. Send (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:52</t>
+    <t>2026-09-03 08:46:27</t>
   </si>
   <si>
     <t>WEB-TC-145</t>
@@ -2764,7 +2764,7 @@
     <t>1. Click clip icon 2. Select diagram.png (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:04</t>
+    <t>2026-09-03 08:46:39</t>
   </si>
   <si>
     <t>WEB-TC-146</t>
@@ -2776,7 +2776,7 @@
     <t>1. Click "Propose Swap" in chat header (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:16</t>
+    <t>2026-09-03 08:46:51</t>
   </si>
   <si>
     <t>WEB-TC-147</t>
@@ -2788,7 +2788,7 @@
     <t>1. Peer views message (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:28</t>
+    <t>2026-09-03 08:47:03</t>
   </si>
   <si>
     <t>WEB-TC-148</t>
@@ -2800,7 +2800,7 @@
     <t>1. Use search bar inside chat thread (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:40</t>
+    <t>2026-09-03 08:47:15</t>
   </si>
   <si>
     <t>WEB-TC-149</t>
@@ -2812,7 +2812,7 @@
     <t>1. Click thread options -&gt; Mute notifications (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:52</t>
+    <t>2026-09-03 08:47:27</t>
   </si>
   <si>
     <t>WEB-TC-150</t>
@@ -2824,7 +2824,7 @@
     <t>1. Open emoji picker 2. Click 👍 (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:04</t>
+    <t>2026-09-03 08:47:39</t>
   </si>
   <si>
     <t>WEB-TC-151</t>
@@ -2836,7 +2836,7 @@
     <t>1. Join call room 2. Allow media devices (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:16</t>
+    <t>2026-09-03 08:47:51</t>
   </si>
   <si>
     <t>WEB-TC-152</t>
@@ -2848,7 +2848,7 @@
     <t>1. Peer enters room 2. Exchange SDP offer/answer (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:28</t>
+    <t>2026-09-03 08:48:03</t>
   </si>
   <si>
     <t>WEB-TC-153</t>
@@ -2860,7 +2860,7 @@
     <t>1. Click Mic button in call toolbar (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:40</t>
+    <t>2026-09-03 08:48:15</t>
   </si>
   <si>
     <t>WEB-TC-154</t>
@@ -2872,7 +2872,7 @@
     <t>1. Click Camera button in toolbar (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:52</t>
+    <t>2026-09-03 08:48:27</t>
   </si>
   <si>
     <t>WEB-TC-155</t>
@@ -2884,7 +2884,7 @@
     <t>1. Click Screen Share 2. Select Window (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:04</t>
+    <t>2026-09-03 08:48:39</t>
   </si>
   <si>
     <t>WEB-TC-156</t>
@@ -2896,7 +2896,7 @@
     <t>1. Open Whiteboard panel 2. Draw line (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:16</t>
+    <t>2026-09-03 08:48:51</t>
   </si>
   <si>
     <t>WEB-TC-157</t>
@@ -2908,7 +2908,7 @@
     <t>1. Click Chat icon during active video call (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:28</t>
+    <t>2026-09-03 08:49:03</t>
   </si>
   <si>
     <t>WEB-TC-158</t>
@@ -2920,7 +2920,7 @@
     <t>1. Monitor WebRTC getStats packet loss (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:40</t>
+    <t>2026-09-03 08:49:15</t>
   </si>
   <si>
     <t>WEB-TC-159</t>
@@ -2932,7 +2932,7 @@
     <t>1. Observe call header timer (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:52</t>
+    <t>2026-09-03 08:49:27</t>
   </si>
   <si>
     <t>WEB-TC-160</t>
@@ -2944,7 +2944,7 @@
     <t>1. Click Red End Call button (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:04</t>
+    <t>2026-09-03 08:49:39</t>
   </si>
   <si>
     <t>WEB-TC-161</t>
@@ -2956,7 +2956,7 @@
     <t>1. Open /schedule 2. View Week view (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:16</t>
+    <t>2026-09-03 08:49:51</t>
   </si>
   <si>
     <t>WEB-TC-162</t>
@@ -2968,7 +2968,7 @@
     <t>1. Click "Set Availability" 2. Mark Mon-Wed 6-8 PM (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:28</t>
+    <t>2026-09-03 08:50:03</t>
   </si>
   <si>
     <t>WEB-TC-163</t>
@@ -2980,7 +2980,7 @@
     <t>1. Pick Tuesday 7:00 PM slot 2. Confirm (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:40</t>
+    <t>2026-09-03 08:50:15</t>
   </si>
   <si>
     <t>WEB-TC-164</t>
@@ -2992,7 +2992,7 @@
     <t>1. Click Reschedule on session 2. Pick new time (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:52</t>
+    <t>2026-09-03 08:50:27</t>
   </si>
   <si>
     <t>WEB-TC-165</t>
@@ -3004,7 +3004,7 @@
     <t>1. Click Cancel 2. Enter reason (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:04</t>
+    <t>2026-09-03 08:50:39</t>
   </si>
   <si>
     <t>WEB-TC-166</t>
@@ -3016,7 +3016,7 @@
     <t>1. Click "Export to .ics" button (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:16</t>
+    <t>2026-09-03 08:50:51</t>
   </si>
   <si>
     <t>WEB-TC-167</t>
@@ -3028,7 +3028,7 @@
     <t>1. Book session with peer in UTC+2 (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:28</t>
+    <t>2026-09-03 08:51:03</t>
   </si>
   <si>
     <t>WEB-TC-168</t>
@@ -3040,7 +3040,7 @@
     <t>1. Attempt booking immediately after session (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:40</t>
+    <t>2026-09-03 08:51:15</t>
   </si>
   <si>
     <t>WEB-TC-169</t>
@@ -3052,7 +3052,7 @@
     <t>1. 10 minutes before booked session (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:52</t>
+    <t>2026-09-03 08:51:27</t>
   </si>
   <si>
     <t>WEB-TC-170</t>
@@ -3064,7 +3064,7 @@
     <t>1. Click Month view pill (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:04</t>
+    <t>2026-09-03 08:51:39</t>
   </si>
   <si>
     <t>WEB-TC-171</t>
@@ -3076,7 +3076,7 @@
     <t>1. Open /profile 2. Edit bio 3. Save (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:16</t>
+    <t>2026-09-03 08:51:51</t>
   </si>
   <si>
     <t>WEB-TC-172</t>
@@ -3088,7 +3088,7 @@
     <t>1. Click avatar 2. Select profile.jpg 3. Crop (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:28</t>
+    <t>2026-09-03 08:52:03</t>
   </si>
   <si>
     <t>WEB-TC-173</t>
@@ -3100,7 +3100,7 @@
     <t>1. Add "Rust" skill 2. Select Expert (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:40</t>
+    <t>2026-09-03 08:52:15</t>
   </si>
   <si>
     <t>WEB-TC-174</t>
@@ -3112,7 +3112,7 @@
     <t>1. Add github repo link 2. Enter title (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:52</t>
+    <t>2026-09-03 08:52:27</t>
   </si>
   <si>
     <t>WEB-TC-175</t>
@@ -3124,7 +3124,7 @@
     <t>1. Scroll to Reviews section (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:04</t>
+    <t>2026-09-03 08:52:39</t>
   </si>
   <si>
     <t>WEB-TC-176</t>
@@ -3136,7 +3136,7 @@
     <t>1. Inspect Badges tab (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:16</t>
+    <t>2026-09-03 08:52:51</t>
   </si>
   <si>
     <t>WEB-TC-177</t>
@@ -3148,7 +3148,7 @@
     <t>1. Click "Share Profile" button (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:28</t>
+    <t>2026-09-03 08:53:03</t>
   </si>
   <si>
     <t>WEB-TC-178</t>
@@ -3160,7 +3160,7 @@
     <t>1. Inspect Skill Credits widget (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:40</t>
+    <t>2026-09-03 08:53:15</t>
   </si>
   <si>
     <t>WEB-TC-179</t>
@@ -3172,7 +3172,7 @@
     <t>1. Visit peer profile 2. Click +1 Endorse on React (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:52</t>
+    <t>2026-09-03 08:53:27</t>
   </si>
   <si>
     <t>WEB-TC-180</t>
@@ -3184,7 +3184,7 @@
     <t>1. Add LinkedIn URL 2. Save profile (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:04</t>
+    <t>2026-09-03 08:53:39</t>
   </si>
   <si>
     <t>WEB-TC-181</t>
@@ -3196,7 +3196,7 @@
     <t>1. Click "Request Swap" on user profile (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:16</t>
+    <t>2026-09-03 08:53:51</t>
   </si>
   <si>
     <t>WEB-TC-182</t>
@@ -3208,7 +3208,7 @@
     <t>1. Open Connections -&gt; Received 2. Click Accept (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:28</t>
+    <t>2026-09-03 08:54:03</t>
   </si>
   <si>
     <t>WEB-TC-183</t>
@@ -3220,7 +3220,7 @@
     <t>1. Click Decline on request (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:40</t>
+    <t>2026-09-03 08:54:15</t>
   </si>
   <si>
     <t>WEB-TC-184</t>
@@ -3232,7 +3232,7 @@
     <t>1. Filter by "Language Exchange" (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:52</t>
+    <t>2026-09-03 08:54:27</t>
   </si>
   <si>
     <t>WEB-TC-185</t>
@@ -3244,7 +3244,7 @@
     <t>1. Search "Sarah" in connections (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:04</t>
+    <t>2026-09-03 08:54:39</t>
   </si>
   <si>
     <t>WEB-TC-186</t>
@@ -3256,7 +3256,7 @@
     <t>1. Click Call icon on active connection (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:16</t>
+    <t>2026-09-03 08:54:51</t>
   </si>
   <si>
     <t>WEB-TC-187</t>
@@ -3268,7 +3268,7 @@
     <t>1. Click Unfriend / Remove connection (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:28</t>
+    <t>2026-09-03 08:55:03</t>
   </si>
   <si>
     <t>WEB-TC-188</t>
@@ -3280,7 +3280,7 @@
     <t>1. View user card with mutual interest (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:40</t>
+    <t>2026-09-03 08:55:15</t>
   </si>
   <si>
     <t>WEB-TC-189</t>
@@ -3292,7 +3292,7 @@
     <t>1. Open Community tab (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:52</t>
+    <t>2026-09-03 08:55:27</t>
   </si>
   <si>
     <t>WEB-TC-190</t>
@@ -3304,7 +3304,7 @@
     <t>1. Enter friend email 2. Click Send Invite (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:04</t>
+    <t>2026-09-03 08:55:39</t>
   </si>
   <si>
     <t>WEB-TC-191</t>
@@ -3316,7 +3316,7 @@
     <t>1. Open Settings -&gt; Security 2. Submit new pass (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:16</t>
+    <t>2026-09-03 08:55:51</t>
   </si>
   <si>
     <t>WEB-TC-192</t>
@@ -3328,7 +3328,7 @@
     <t>1. Toggle 2FA 2. Scan QR 3. Enter 6-digit code (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:28</t>
+    <t>2026-09-03 08:56:03</t>
   </si>
   <si>
     <t>WEB-TC-193</t>
@@ -3340,7 +3340,7 @@
     <t>1. Uncheck "Marketing emails" 2. Save (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:40</t>
+    <t>2026-09-03 08:56:15</t>
   </si>
   <si>
     <t>WEB-TC-194</t>
@@ -3352,7 +3352,7 @@
     <t>1. Toggle sound on/off (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:52</t>
+    <t>2026-09-03 08:56:27</t>
   </si>
   <si>
     <t>WEB-TC-195</t>
@@ -3364,7 +3364,7 @@
     <t>1. Toggle "Private Profile" switch (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:04</t>
+    <t>2026-09-03 08:56:39</t>
   </si>
   <si>
     <t>WEB-TC-196</t>
@@ -3376,7 +3376,7 @@
     <t>1. Click "Request Data Archive" (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:16</t>
+    <t>2026-09-03 08:56:51</t>
   </si>
   <si>
     <t>WEB-TC-197</t>
@@ -3388,7 +3388,7 @@
     <t>1. View Blocked Users 2. Click Unblock (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:28</t>
+    <t>2026-09-03 08:57:03</t>
   </si>
   <si>
     <t>WEB-TC-198</t>
@@ -3400,7 +3400,7 @@
     <t>1. Click Delete Account 2. Type "DELETE" (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:40</t>
+    <t>2026-09-03 08:57:15</t>
   </si>
   <si>
     <t>WEB-TC-199</t>
@@ -3412,7 +3412,7 @@
     <t>1. Change language to Spanish (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:52</t>
+    <t>2026-09-03 08:57:27</t>
   </si>
   <si>
     <t>WEB-TC-200</t>
@@ -3424,7 +3424,7 @@
     <t>1. Click "Clear Cache" in settings (Viewport: 390x844 (Mobile Chrome Emulation))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:04</t>
+    <t>2026-09-03 08:57:39</t>
   </si>
   <si>
     <t>WEB-TC-201</t>
@@ -3436,7 +3436,7 @@
     <t>1. Navigate to /signup 2. Fill inputs 3. Submit (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:16</t>
+    <t>2026-09-03 08:57:51</t>
   </si>
   <si>
     <t>WEB-TC-202</t>
@@ -3448,7 +3448,7 @@
     <t>1. Enter weak vs strong password 2. Check meter (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:28</t>
+    <t>2026-09-03 08:58:03</t>
   </si>
   <si>
     <t>WEB-TC-203</t>
@@ -3460,7 +3460,7 @@
     <t>1. Enter existing email 2. Submit form (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:40</t>
+    <t>2026-09-03 08:58:15</t>
   </si>
   <si>
     <t>WEB-TC-204</t>
@@ -3472,7 +3472,7 @@
     <t>1. Uncheck terms 2. Click sign up (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:52</t>
+    <t>2026-09-03 08:58:27</t>
   </si>
   <si>
     <t>WEB-TC-205</t>
@@ -3484,7 +3484,7 @@
     <t>1. Click Continue with Google (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:04</t>
+    <t>2026-09-03 08:58:39</t>
   </si>
   <si>
     <t>WEB-TC-206</t>
@@ -3496,7 +3496,7 @@
     <t>1. Select 3 offer skills 2. Click Next (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:16</t>
+    <t>2026-09-03 08:58:51</t>
   </si>
   <si>
     <t>WEB-TC-207</t>
@@ -3508,7 +3508,7 @@
     <t>1. Select 2 learn skills 2. Click Complete (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:28</t>
+    <t>2026-09-03 08:59:03</t>
   </si>
   <si>
     <t>WEB-TC-208</t>
@@ -3520,7 +3520,7 @@
     <t>1. Click Skip for now (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:40</t>
+    <t>2026-09-03 08:59:15</t>
   </si>
   <si>
     <t>WEB-TC-209</t>
@@ -3532,7 +3532,7 @@
     <t>1. Open /signup (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:52</t>
+    <t>2026-09-03 08:59:27</t>
   </si>
   <si>
     <t>WEB-TC-210</t>
@@ -3544,7 +3544,7 @@
     <t>1. Type password 2. Toggle eye icon (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:04</t>
+    <t>2026-09-03 08:59:39</t>
   </si>
   <si>
     <t>WEB-TC-211</t>
@@ -3556,7 +3556,7 @@
     <t>1. Navigate to /login 2. Submit credentials (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:16</t>
+    <t>2026-09-03 08:59:51</t>
   </si>
   <si>
     <t>WEB-TC-212</t>
@@ -3568,7 +3568,7 @@
     <t>1. Enter valid email, wrong password (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:28</t>
+    <t>2026-09-03 09:00:03</t>
   </si>
   <si>
     <t>WEB-TC-213</t>
@@ -3580,7 +3580,7 @@
     <t>1. Enter unregistered email (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:40</t>
+    <t>2026-09-03 09:00:15</t>
   </si>
   <si>
     <t>WEB-TC-214</t>
@@ -3592,7 +3592,7 @@
     <t>1. Check Remember me 2. Login 3. Reopen browser (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:52</t>
+    <t>2026-09-03 09:00:27</t>
   </si>
   <si>
     <t>WEB-TC-215</t>
@@ -3604,7 +3604,7 @@
     <t>1. Click Forgot Password 2. Enter email (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:04</t>
+    <t>2026-09-03 09:00:39</t>
   </si>
   <si>
     <t>WEB-TC-216</t>
@@ -3616,7 +3616,7 @@
     <t>1. Directly open /dashboard as unauthenticated (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:16</t>
+    <t>2026-09-03 09:00:51</t>
   </si>
   <si>
     <t>WEB-TC-217</t>
@@ -3628,7 +3628,7 @@
     <t>1. Access /settings?tab=security 2. Login (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:28</t>
+    <t>2026-09-03 09:01:03</t>
   </si>
   <si>
     <t>WEB-TC-218</t>
@@ -3640,7 +3640,7 @@
     <t>1. Click User Menu -&gt; Logout (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:40</t>
+    <t>2026-09-03 09:01:15</t>
   </si>
   <si>
     <t>WEB-TC-219</t>
@@ -3652,7 +3652,7 @@
     <t>1. Logout in Tab A 2. Observe Tab B (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:52</t>
+    <t>2026-09-03 09:01:27</t>
   </si>
   <si>
     <t>WEB-TC-220</t>
@@ -3664,7 +3664,7 @@
     <t>1. Wait for token expiration simulation (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:04</t>
+    <t>2026-09-03 09:01:39</t>
   </si>
   <si>
     <t>WEB-TC-221</t>
@@ -3676,7 +3676,7 @@
     <t>1. Open dashboard 2. Inspect stats cards (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:16</t>
+    <t>2026-09-03 09:01:51</t>
   </si>
   <si>
     <t>WEB-TC-222</t>
@@ -3688,7 +3688,7 @@
     <t>1. Scroll to Matches section (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:28</t>
+    <t>2026-09-03 09:02:03</t>
   </si>
   <si>
     <t>WEB-TC-223</t>
@@ -3700,7 +3700,7 @@
     <t>1. Check Upcoming Sessions block (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:40</t>
+    <t>2026-09-03 09:02:15</t>
   </si>
   <si>
     <t>WEB-TC-224</t>
@@ -3712,7 +3712,7 @@
     <t>1. Click Quick Connect on match card (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:52</t>
+    <t>2026-09-03 09:02:27</t>
   </si>
   <si>
     <t>WEB-TC-225</t>
@@ -3724,7 +3724,7 @@
     <t>1. Click Accept on incoming card (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:04</t>
+    <t>2026-09-03 09:02:39</t>
   </si>
   <si>
     <t>WEB-TC-226</t>
@@ -3736,7 +3736,7 @@
     <t>1. Click next arrow on carousel (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:16</t>
+    <t>2026-09-03 09:02:51</t>
   </si>
   <si>
     <t>WEB-TC-227</t>
@@ -3748,7 +3748,7 @@
     <t>1. Click "Figma" badge (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:28</t>
+    <t>2026-09-03 09:03:03</t>
   </si>
   <si>
     <t>WEB-TC-228</t>
@@ -3760,7 +3760,7 @@
     <t>1. Resize viewport to 768px (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:40</t>
+    <t>2026-09-03 09:03:15</t>
   </si>
   <si>
     <t>WEB-TC-229</t>
@@ -3772,7 +3772,7 @@
     <t>1. Click Dark Mode button 2. Refresh page (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:52</t>
+    <t>2026-09-03 09:03:27</t>
   </si>
   <si>
     <t>WEB-TC-230</t>
@@ -3784,7 +3784,7 @@
     <t>1. Trigger incoming swap request event (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:04</t>
+    <t>2026-09-03 09:03:39</t>
   </si>
   <si>
     <t>WEB-TC-231</t>
@@ -3796,7 +3796,7 @@
     <t>1. Type "Py" in search box (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:16</t>
+    <t>2026-09-03 09:03:51</t>
   </si>
   <si>
     <t>WEB-TC-232</t>
@@ -3808,7 +3808,7 @@
     <t>1. Select "Design" category pill (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:28</t>
+    <t>2026-09-03 09:04:03</t>
   </si>
   <si>
     <t>WEB-TC-233</t>
@@ -3820,7 +3820,7 @@
     <t>1. Toggle "Weekends" filter (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:40</t>
+    <t>2026-09-03 09:04:15</t>
   </si>
   <si>
     <t>WEB-TC-234</t>
@@ -3832,7 +3832,7 @@
     <t>1. Select Sort: Top Rated (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:52</t>
+    <t>2026-09-03 09:04:27</t>
   </si>
   <si>
     <t>WEB-TC-235</t>
@@ -3844,7 +3844,7 @@
     <t>1. Select Sort: Fastest Response (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:04</t>
+    <t>2026-09-03 09:04:39</t>
   </si>
   <si>
     <t>WEB-TC-236</t>
@@ -3856,7 +3856,7 @@
     <t>1. Drag slider to Advanced/Expert (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:16</t>
+    <t>2026-09-03 09:04:51</t>
   </si>
   <si>
     <t>WEB-TC-237</t>
@@ -3868,7 +3868,7 @@
     <t>1. Click on user card in grid (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:28</t>
+    <t>2026-09-03 09:05:03</t>
   </si>
   <si>
     <t>WEB-TC-238</t>
@@ -3880,7 +3880,7 @@
     <t>1. Search "xyz123nonsense" (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:40</t>
+    <t>2026-09-03 09:05:15</t>
   </si>
   <si>
     <t>WEB-TC-239</t>
@@ -3892,7 +3892,7 @@
     <t>1. Perform search with filters 2. Check URL (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:52</t>
+    <t>2026-09-03 09:05:27</t>
   </si>
   <si>
     <t>WEB-TC-240</t>
@@ -3904,7 +3904,7 @@
     <t>1. Scroll to bottom of 20 results (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:04</t>
+    <t>2026-09-03 09:05:39</t>
   </si>
   <si>
     <t>WEB-TC-241</t>
@@ -3916,7 +3916,7 @@
     <t>1. Open /messages 2. Inspect threads (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:16</t>
+    <t>2026-09-03 09:05:51</t>
   </si>
   <si>
     <t>WEB-TC-242</t>
@@ -3928,7 +3928,7 @@
     <t>1. Type "Hello let's swap!" 2. Press Enter (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:28</t>
+    <t>2026-09-03 09:06:03</t>
   </si>
   <si>
     <t>WEB-TC-243</t>
@@ -3940,7 +3940,7 @@
     <t>1. Simulate peer typing event (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:40</t>
+    <t>2026-09-03 09:06:15</t>
   </si>
   <si>
     <t>WEB-TC-244</t>
@@ -3952,7 +3952,7 @@
     <t>1. Paste code block in chat 2. Send (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:52</t>
+    <t>2026-09-03 09:06:27</t>
   </si>
   <si>
     <t>WEB-TC-245</t>
@@ -3964,7 +3964,7 @@
     <t>1. Click clip icon 2. Select diagram.png (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:04</t>
+    <t>2026-09-03 09:06:39</t>
   </si>
   <si>
     <t>WEB-TC-246</t>
@@ -3976,7 +3976,7 @@
     <t>1. Click "Propose Swap" in chat header (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:16</t>
+    <t>2026-09-03 09:06:51</t>
   </si>
   <si>
     <t>WEB-TC-247</t>
@@ -3988,7 +3988,7 @@
     <t>1. Peer views message (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:28</t>
+    <t>2026-09-03 09:07:03</t>
   </si>
   <si>
     <t>WEB-TC-248</t>
@@ -4000,7 +4000,7 @@
     <t>1. Use search bar inside chat thread (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:40</t>
+    <t>2026-09-03 09:07:15</t>
   </si>
   <si>
     <t>WEB-TC-249</t>
@@ -4012,7 +4012,7 @@
     <t>1. Click thread options -&gt; Mute notifications (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:52</t>
+    <t>2026-09-03 09:07:27</t>
   </si>
   <si>
     <t>WEB-TC-250</t>
@@ -4024,7 +4024,7 @@
     <t>1. Open emoji picker 2. Click 👍 (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:04</t>
+    <t>2026-09-03 09:07:39</t>
   </si>
   <si>
     <t>WEB-TC-251</t>
@@ -4036,7 +4036,7 @@
     <t>1. Join call room 2. Allow media devices (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:16</t>
+    <t>2026-09-03 09:07:51</t>
   </si>
   <si>
     <t>WEB-TC-252</t>
@@ -4048,7 +4048,7 @@
     <t>1. Peer enters room 2. Exchange SDP offer/answer (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:28</t>
+    <t>2026-09-03 09:08:03</t>
   </si>
   <si>
     <t>WEB-TC-253</t>
@@ -4060,7 +4060,7 @@
     <t>1. Click Mic button in call toolbar (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:40</t>
+    <t>2026-09-03 09:08:15</t>
   </si>
   <si>
     <t>WEB-TC-254</t>
@@ -4072,7 +4072,7 @@
     <t>1. Click Camera button in toolbar (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:52</t>
+    <t>2026-09-03 09:08:27</t>
   </si>
   <si>
     <t>WEB-TC-255</t>
@@ -4084,7 +4084,7 @@
     <t>1. Click Screen Share 2. Select Window (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:04</t>
+    <t>2026-09-03 09:08:39</t>
   </si>
   <si>
     <t>WEB-TC-256</t>
@@ -4096,7 +4096,7 @@
     <t>1. Open Whiteboard panel 2. Draw line (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:16</t>
+    <t>2026-09-03 09:08:51</t>
   </si>
   <si>
     <t>WEB-TC-257</t>
@@ -4108,7 +4108,7 @@
     <t>1. Click Chat icon during active video call (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:28</t>
+    <t>2026-09-03 09:09:03</t>
   </si>
   <si>
     <t>WEB-TC-258</t>
@@ -4120,7 +4120,7 @@
     <t>1. Monitor WebRTC getStats packet loss (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:40</t>
+    <t>2026-09-03 09:09:15</t>
   </si>
   <si>
     <t>WEB-TC-259</t>
@@ -4132,7 +4132,7 @@
     <t>1. Observe call header timer (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:52</t>
+    <t>2026-09-03 09:09:27</t>
   </si>
   <si>
     <t>WEB-TC-260</t>
@@ -4144,7 +4144,7 @@
     <t>1. Click Red End Call button (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:04</t>
+    <t>2026-09-03 09:09:39</t>
   </si>
   <si>
     <t>WEB-TC-261</t>
@@ -4156,7 +4156,7 @@
     <t>1. Open /schedule 2. View Week view (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:16</t>
+    <t>2026-09-03 09:09:51</t>
   </si>
   <si>
     <t>WEB-TC-262</t>
@@ -4168,7 +4168,7 @@
     <t>1. Click "Set Availability" 2. Mark Mon-Wed 6-8 PM (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:28</t>
+    <t>2026-09-03 09:10:03</t>
   </si>
   <si>
     <t>WEB-TC-263</t>
@@ -4180,7 +4180,7 @@
     <t>1. Pick Tuesday 7:00 PM slot 2. Confirm (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:40</t>
+    <t>2026-09-03 09:10:15</t>
   </si>
   <si>
     <t>WEB-TC-264</t>
@@ -4192,7 +4192,7 @@
     <t>1. Click Reschedule on session 2. Pick new time (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:52</t>
+    <t>2026-09-03 09:10:27</t>
   </si>
   <si>
     <t>WEB-TC-265</t>
@@ -4204,7 +4204,7 @@
     <t>1. Click Cancel 2. Enter reason (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:04</t>
+    <t>2026-09-03 09:10:39</t>
   </si>
   <si>
     <t>WEB-TC-266</t>
@@ -4216,7 +4216,7 @@
     <t>1. Click "Export to .ics" button (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:16</t>
+    <t>2026-09-03 09:10:51</t>
   </si>
   <si>
     <t>WEB-TC-267</t>
@@ -4228,7 +4228,7 @@
     <t>1. Book session with peer in UTC+2 (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:28</t>
+    <t>2026-09-03 09:11:03</t>
   </si>
   <si>
     <t>WEB-TC-268</t>
@@ -4240,7 +4240,7 @@
     <t>1. Attempt booking immediately after session (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:40</t>
+    <t>2026-09-03 09:11:15</t>
   </si>
   <si>
     <t>WEB-TC-269</t>
@@ -4252,7 +4252,7 @@
     <t>1. 10 minutes before booked session (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:52</t>
+    <t>2026-09-03 09:11:27</t>
   </si>
   <si>
     <t>WEB-TC-270</t>
@@ -4264,7 +4264,7 @@
     <t>1. Click Month view pill (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:04</t>
+    <t>2026-09-03 09:11:39</t>
   </si>
   <si>
     <t>WEB-TC-271</t>
@@ -4276,7 +4276,7 @@
     <t>1. Open /profile 2. Edit bio 3. Save (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:16</t>
+    <t>2026-09-03 09:11:51</t>
   </si>
   <si>
     <t>WEB-TC-272</t>
@@ -4288,7 +4288,7 @@
     <t>1. Click avatar 2. Select profile.jpg 3. Crop (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:28</t>
+    <t>2026-09-03 09:12:03</t>
   </si>
   <si>
     <t>WEB-TC-273</t>
@@ -4300,7 +4300,7 @@
     <t>1. Add "Rust" skill 2. Select Expert (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:40</t>
+    <t>2026-09-03 09:12:15</t>
   </si>
   <si>
     <t>WEB-TC-274</t>
@@ -4312,7 +4312,7 @@
     <t>1. Add github repo link 2. Enter title (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:52</t>
+    <t>2026-09-03 09:12:27</t>
   </si>
   <si>
     <t>WEB-TC-275</t>
@@ -4324,7 +4324,7 @@
     <t>1. Scroll to Reviews section (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:04</t>
+    <t>2026-09-03 09:12:39</t>
   </si>
   <si>
     <t>WEB-TC-276</t>
@@ -4336,7 +4336,7 @@
     <t>1. Inspect Badges tab (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:16</t>
+    <t>2026-09-03 09:12:51</t>
   </si>
   <si>
     <t>WEB-TC-277</t>
@@ -4348,7 +4348,7 @@
     <t>1. Click "Share Profile" button (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:28</t>
+    <t>2026-09-03 09:13:03</t>
   </si>
   <si>
     <t>WEB-TC-278</t>
@@ -4360,7 +4360,7 @@
     <t>1. Inspect Skill Credits widget (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:40</t>
+    <t>2026-09-03 09:13:15</t>
   </si>
   <si>
     <t>WEB-TC-279</t>
@@ -4372,7 +4372,7 @@
     <t>1. Visit peer profile 2. Click +1 Endorse on React (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:52</t>
+    <t>2026-09-03 09:13:27</t>
   </si>
   <si>
     <t>WEB-TC-280</t>
@@ -4384,7 +4384,7 @@
     <t>1. Add LinkedIn URL 2. Save profile (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:04</t>
+    <t>2026-09-03 09:13:39</t>
   </si>
   <si>
     <t>WEB-TC-281</t>
@@ -4396,7 +4396,7 @@
     <t>1. Click "Request Swap" on user profile (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:16</t>
+    <t>2026-09-03 09:13:51</t>
   </si>
   <si>
     <t>WEB-TC-282</t>
@@ -4408,7 +4408,7 @@
     <t>1. Open Connections -&gt; Received 2. Click Accept (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:28</t>
+    <t>2026-09-03 09:14:03</t>
   </si>
   <si>
     <t>WEB-TC-283</t>
@@ -4420,7 +4420,7 @@
     <t>1. Click Decline on request (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:40</t>
+    <t>2026-09-03 09:14:15</t>
   </si>
   <si>
     <t>WEB-TC-284</t>
@@ -4432,7 +4432,7 @@
     <t>1. Filter by "Language Exchange" (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:52</t>
+    <t>2026-09-03 09:14:27</t>
   </si>
   <si>
     <t>WEB-TC-285</t>
@@ -4444,7 +4444,7 @@
     <t>1. Search "Sarah" in connections (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:04</t>
+    <t>2026-09-03 09:14:39</t>
   </si>
   <si>
     <t>WEB-TC-286</t>
@@ -4456,7 +4456,7 @@
     <t>1. Click Call icon on active connection (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:16</t>
+    <t>2026-09-03 09:14:51</t>
   </si>
   <si>
     <t>WEB-TC-287</t>
@@ -4468,7 +4468,7 @@
     <t>1. Click Unfriend / Remove connection (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:28</t>
+    <t>2026-09-03 09:15:03</t>
   </si>
   <si>
     <t>WEB-TC-288</t>
@@ -4480,7 +4480,7 @@
     <t>1. View user card with mutual interest (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:40</t>
+    <t>2026-09-03 09:15:15</t>
   </si>
   <si>
     <t>WEB-TC-289</t>
@@ -4492,7 +4492,7 @@
     <t>1. Open Community tab (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:52</t>
+    <t>2026-09-03 09:15:27</t>
   </si>
   <si>
     <t>WEB-TC-290</t>
@@ -4504,7 +4504,7 @@
     <t>1. Enter friend email 2. Click Send Invite (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:04</t>
+    <t>2026-09-03 09:15:39</t>
   </si>
   <si>
     <t>WEB-TC-291</t>
@@ -4516,7 +4516,7 @@
     <t>1. Open Settings -&gt; Security 2. Submit new pass (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:16</t>
+    <t>2026-09-03 09:15:51</t>
   </si>
   <si>
     <t>WEB-TC-292</t>
@@ -4528,7 +4528,7 @@
     <t>1. Toggle 2FA 2. Scan QR 3. Enter 6-digit code (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:28</t>
+    <t>2026-09-03 09:16:03</t>
   </si>
   <si>
     <t>WEB-TC-293</t>
@@ -4540,7 +4540,7 @@
     <t>1. Uncheck "Marketing emails" 2. Save (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:40</t>
+    <t>2026-09-03 09:16:15</t>
   </si>
   <si>
     <t>WEB-TC-294</t>
@@ -4552,7 +4552,7 @@
     <t>1. Toggle sound on/off (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:52</t>
+    <t>2026-09-03 09:16:27</t>
   </si>
   <si>
     <t>WEB-TC-295</t>
@@ -4564,7 +4564,7 @@
     <t>1. Toggle "Private Profile" switch (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:04</t>
+    <t>2026-09-03 09:16:39</t>
   </si>
   <si>
     <t>WEB-TC-296</t>
@@ -4576,7 +4576,7 @@
     <t>1. Click "Request Data Archive" (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:16</t>
+    <t>2026-09-03 09:16:51</t>
   </si>
   <si>
     <t>WEB-TC-297</t>
@@ -4588,7 +4588,7 @@
     <t>1. View Blocked Users 2. Click Unblock (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:28</t>
+    <t>2026-09-03 09:17:03</t>
   </si>
   <si>
     <t>WEB-TC-298</t>
@@ -4600,7 +4600,7 @@
     <t>1. Click Delete Account 2. Type "DELETE" (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:40</t>
+    <t>2026-09-03 09:17:15</t>
   </si>
   <si>
     <t>WEB-TC-299</t>
@@ -4612,7 +4612,7 @@
     <t>1. Change language to Spanish (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:52</t>
+    <t>2026-09-03 09:17:27</t>
   </si>
   <si>
     <t>WEB-TC-300</t>
@@ -4624,7 +4624,7 @@
     <t>1. Click "Clear Cache" in settings (Network: Simulated 3G Latency (200ms))</t>
   </si>
   <si>
-    <t>2026-09-03 09:10:04</t>
+    <t>2026-09-03 09:17:39</t>
   </si>
 </sst>
 </file>
@@ -5166,7 +5166,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="2">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -5207,7 +5207,7 @@
         <v>30</v>
       </c>
       <c r="J3" s="5">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>22</v>
@@ -5248,7 +5248,7 @@
         <v>38</v>
       </c>
       <c r="J4" s="2">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>22</v>
@@ -5289,7 +5289,7 @@
         <v>45</v>
       </c>
       <c r="J5" s="5">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>22</v>
@@ -5330,7 +5330,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="2">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>22</v>
@@ -5412,7 +5412,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="2">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>22</v>
@@ -5453,7 +5453,7 @@
         <v>74</v>
       </c>
       <c r="J9" s="5">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>22</v>
@@ -5494,7 +5494,7 @@
         <v>81</v>
       </c>
       <c r="J10" s="2">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>22</v>
@@ -5535,7 +5535,7 @@
         <v>88</v>
       </c>
       <c r="J11" s="5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>22</v>
@@ -5576,7 +5576,7 @@
         <v>97</v>
       </c>
       <c r="J12" s="2">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>22</v>
@@ -5617,7 +5617,7 @@
         <v>104</v>
       </c>
       <c r="J13" s="5">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>22</v>
@@ -5658,7 +5658,7 @@
         <v>111</v>
       </c>
       <c r="J14" s="2">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>22</v>
@@ -5699,7 +5699,7 @@
         <v>118</v>
       </c>
       <c r="J15" s="5">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>22</v>
@@ -5740,7 +5740,7 @@
         <v>125</v>
       </c>
       <c r="J16" s="2">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>22</v>
@@ -5781,7 +5781,7 @@
         <v>132</v>
       </c>
       <c r="J17" s="5">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>22</v>
@@ -5822,7 +5822,7 @@
         <v>139</v>
       </c>
       <c r="J18" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>22</v>
@@ -5863,7 +5863,7 @@
         <v>146</v>
       </c>
       <c r="J19" s="5">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>22</v>
@@ -5904,7 +5904,7 @@
         <v>153</v>
       </c>
       <c r="J20" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>22</v>
@@ -5945,7 +5945,7 @@
         <v>160</v>
       </c>
       <c r="J21" s="5">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>22</v>
@@ -5986,7 +5986,7 @@
         <v>169</v>
       </c>
       <c r="J22" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>22</v>
@@ -6027,7 +6027,7 @@
         <v>176</v>
       </c>
       <c r="J23" s="5">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>22</v>
@@ -6068,7 +6068,7 @@
         <v>183</v>
       </c>
       <c r="J24" s="2">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>22</v>
@@ -6109,7 +6109,7 @@
         <v>190</v>
       </c>
       <c r="J25" s="5">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>22</v>
@@ -6150,7 +6150,7 @@
         <v>197</v>
       </c>
       <c r="J26" s="2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>22</v>
@@ -6191,7 +6191,7 @@
         <v>204</v>
       </c>
       <c r="J27" s="5">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>22</v>
@@ -6232,7 +6232,7 @@
         <v>211</v>
       </c>
       <c r="J28" s="2">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>22</v>
@@ -6273,7 +6273,7 @@
         <v>218</v>
       </c>
       <c r="J29" s="5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>22</v>
@@ -6314,7 +6314,7 @@
         <v>225</v>
       </c>
       <c r="J30" s="2">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>22</v>
@@ -6355,7 +6355,7 @@
         <v>232</v>
       </c>
       <c r="J31" s="5">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>22</v>
@@ -6396,7 +6396,7 @@
         <v>241</v>
       </c>
       <c r="J32" s="2">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>22</v>
@@ -6437,7 +6437,7 @@
         <v>248</v>
       </c>
       <c r="J33" s="5">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>22</v>
@@ -6478,7 +6478,7 @@
         <v>255</v>
       </c>
       <c r="J34" s="2">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>22</v>
@@ -6519,7 +6519,7 @@
         <v>262</v>
       </c>
       <c r="J35" s="5">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>22</v>
@@ -6560,7 +6560,7 @@
         <v>269</v>
       </c>
       <c r="J36" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>22</v>
@@ -6601,7 +6601,7 @@
         <v>276</v>
       </c>
       <c r="J37" s="5">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>22</v>
@@ -6642,7 +6642,7 @@
         <v>283</v>
       </c>
       <c r="J38" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>22</v>
@@ -6683,7 +6683,7 @@
         <v>290</v>
       </c>
       <c r="J39" s="5">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>22</v>
@@ -6724,7 +6724,7 @@
         <v>297</v>
       </c>
       <c r="J40" s="2">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>22</v>
@@ -6765,7 +6765,7 @@
         <v>304</v>
       </c>
       <c r="J41" s="5">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>22</v>
@@ -6806,7 +6806,7 @@
         <v>313</v>
       </c>
       <c r="J42" s="2">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>22</v>
@@ -6847,7 +6847,7 @@
         <v>320</v>
       </c>
       <c r="J43" s="5">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>22</v>
@@ -6929,7 +6929,7 @@
         <v>334</v>
       </c>
       <c r="J45" s="5">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>22</v>
@@ -6970,7 +6970,7 @@
         <v>341</v>
       </c>
       <c r="J46" s="2">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>22</v>
@@ -7011,7 +7011,7 @@
         <v>348</v>
       </c>
       <c r="J47" s="5">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>22</v>
@@ -7052,7 +7052,7 @@
         <v>355</v>
       </c>
       <c r="J48" s="2">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>22</v>
@@ -7093,7 +7093,7 @@
         <v>362</v>
       </c>
       <c r="J49" s="5">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>22</v>
@@ -7134,7 +7134,7 @@
         <v>369</v>
       </c>
       <c r="J50" s="2">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>22</v>
@@ -7175,7 +7175,7 @@
         <v>376</v>
       </c>
       <c r="J51" s="5">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>22</v>
@@ -7216,7 +7216,7 @@
         <v>385</v>
       </c>
       <c r="J52" s="2">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>22</v>
@@ -7257,7 +7257,7 @@
         <v>392</v>
       </c>
       <c r="J53" s="5">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>22</v>
@@ -7298,7 +7298,7 @@
         <v>399</v>
       </c>
       <c r="J54" s="2">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>22</v>
@@ -7339,7 +7339,7 @@
         <v>406</v>
       </c>
       <c r="J55" s="5">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>22</v>
@@ -7380,7 +7380,7 @@
         <v>413</v>
       </c>
       <c r="J56" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>22</v>
@@ -7421,7 +7421,7 @@
         <v>420</v>
       </c>
       <c r="J57" s="5">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>22</v>
@@ -7462,7 +7462,7 @@
         <v>427</v>
       </c>
       <c r="J58" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>22</v>
@@ -7503,7 +7503,7 @@
         <v>434</v>
       </c>
       <c r="J59" s="5">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>22</v>
@@ -7544,7 +7544,7 @@
         <v>441</v>
       </c>
       <c r="J60" s="2">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>22</v>
@@ -7585,7 +7585,7 @@
         <v>448</v>
       </c>
       <c r="J61" s="5">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>22</v>
@@ -7626,7 +7626,7 @@
         <v>457</v>
       </c>
       <c r="J62" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>22</v>
@@ -7667,7 +7667,7 @@
         <v>464</v>
       </c>
       <c r="J63" s="5">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>22</v>
@@ -7708,7 +7708,7 @@
         <v>471</v>
       </c>
       <c r="J64" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>22</v>
@@ -7749,7 +7749,7 @@
         <v>478</v>
       </c>
       <c r="J65" s="5">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>22</v>
@@ -7790,7 +7790,7 @@
         <v>485</v>
       </c>
       <c r="J66" s="2">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>22</v>
@@ -7831,7 +7831,7 @@
         <v>492</v>
       </c>
       <c r="J67" s="5">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>22</v>
@@ -7872,7 +7872,7 @@
         <v>499</v>
       </c>
       <c r="J68" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>22</v>
@@ -7913,7 +7913,7 @@
         <v>506</v>
       </c>
       <c r="J69" s="5">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>22</v>
@@ -7954,7 +7954,7 @@
         <v>513</v>
       </c>
       <c r="J70" s="2">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>22</v>
@@ -7995,7 +7995,7 @@
         <v>520</v>
       </c>
       <c r="J71" s="5">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>22</v>
@@ -8036,7 +8036,7 @@
         <v>529</v>
       </c>
       <c r="J72" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>22</v>
@@ -8077,7 +8077,7 @@
         <v>536</v>
       </c>
       <c r="J73" s="5">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>22</v>
@@ -8118,7 +8118,7 @@
         <v>543</v>
       </c>
       <c r="J74" s="2">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>22</v>
@@ -8159,7 +8159,7 @@
         <v>550</v>
       </c>
       <c r="J75" s="5">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>22</v>
@@ -8200,7 +8200,7 @@
         <v>557</v>
       </c>
       <c r="J76" s="2">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>22</v>
@@ -8241,7 +8241,7 @@
         <v>564</v>
       </c>
       <c r="J77" s="5">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>22</v>
@@ -8282,7 +8282,7 @@
         <v>571</v>
       </c>
       <c r="J78" s="2">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>22</v>
@@ -8323,7 +8323,7 @@
         <v>578</v>
       </c>
       <c r="J79" s="5">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>22</v>
@@ -8364,7 +8364,7 @@
         <v>585</v>
       </c>
       <c r="J80" s="2">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>22</v>
@@ -8405,7 +8405,7 @@
         <v>592</v>
       </c>
       <c r="J81" s="5">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>22</v>
@@ -8446,7 +8446,7 @@
         <v>601</v>
       </c>
       <c r="J82" s="2">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>22</v>
@@ -8487,7 +8487,7 @@
         <v>608</v>
       </c>
       <c r="J83" s="5">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>22</v>
@@ -8528,7 +8528,7 @@
         <v>615</v>
       </c>
       <c r="J84" s="2">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>22</v>
@@ -8569,7 +8569,7 @@
         <v>622</v>
       </c>
       <c r="J85" s="5">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>22</v>
@@ -8610,7 +8610,7 @@
         <v>629</v>
       </c>
       <c r="J86" s="2">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>22</v>
@@ -8651,7 +8651,7 @@
         <v>636</v>
       </c>
       <c r="J87" s="5">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>22</v>
@@ -8692,7 +8692,7 @@
         <v>643</v>
       </c>
       <c r="J88" s="2">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>22</v>
@@ -8733,7 +8733,7 @@
         <v>650</v>
       </c>
       <c r="J89" s="5">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>22</v>
@@ -8774,7 +8774,7 @@
         <v>657</v>
       </c>
       <c r="J90" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>22</v>
@@ -8815,7 +8815,7 @@
         <v>664</v>
       </c>
       <c r="J91" s="5">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>22</v>
@@ -8856,7 +8856,7 @@
         <v>673</v>
       </c>
       <c r="J92" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>22</v>
@@ -8897,7 +8897,7 @@
         <v>680</v>
       </c>
       <c r="J93" s="5">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>22</v>
@@ -8938,7 +8938,7 @@
         <v>687</v>
       </c>
       <c r="J94" s="2">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>22</v>
@@ -8979,7 +8979,7 @@
         <v>694</v>
       </c>
       <c r="J95" s="5">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>22</v>
@@ -9020,7 +9020,7 @@
         <v>701</v>
       </c>
       <c r="J96" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>22</v>
@@ -9061,7 +9061,7 @@
         <v>708</v>
       </c>
       <c r="J97" s="5">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>22</v>
@@ -9102,7 +9102,7 @@
         <v>715</v>
       </c>
       <c r="J98" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>22</v>
@@ -9143,7 +9143,7 @@
         <v>722</v>
       </c>
       <c r="J99" s="5">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>22</v>
@@ -9184,7 +9184,7 @@
         <v>729</v>
       </c>
       <c r="J100" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>22</v>
@@ -9225,7 +9225,7 @@
         <v>736</v>
       </c>
       <c r="J101" s="5">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>22</v>
@@ -9266,7 +9266,7 @@
         <v>21</v>
       </c>
       <c r="J102" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>22</v>
@@ -9307,7 +9307,7 @@
         <v>30</v>
       </c>
       <c r="J103" s="5">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>22</v>
@@ -9348,7 +9348,7 @@
         <v>38</v>
       </c>
       <c r="J104" s="2">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>22</v>
@@ -9389,7 +9389,7 @@
         <v>45</v>
       </c>
       <c r="J105" s="5">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>22</v>
@@ -9430,7 +9430,7 @@
         <v>52</v>
       </c>
       <c r="J106" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>22</v>
@@ -9471,7 +9471,7 @@
         <v>60</v>
       </c>
       <c r="J107" s="5">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>22</v>
@@ -9512,7 +9512,7 @@
         <v>67</v>
       </c>
       <c r="J108" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>22</v>
@@ -9553,7 +9553,7 @@
         <v>74</v>
       </c>
       <c r="J109" s="5">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>22</v>
@@ -9594,7 +9594,7 @@
         <v>81</v>
       </c>
       <c r="J110" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>22</v>
@@ -9635,7 +9635,7 @@
         <v>88</v>
       </c>
       <c r="J111" s="5">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>22</v>
@@ -9676,7 +9676,7 @@
         <v>97</v>
       </c>
       <c r="J112" s="2">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>22</v>
@@ -9717,7 +9717,7 @@
         <v>104</v>
       </c>
       <c r="J113" s="5">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>22</v>
@@ -9758,7 +9758,7 @@
         <v>111</v>
       </c>
       <c r="J114" s="2">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>22</v>
@@ -9799,7 +9799,7 @@
         <v>118</v>
       </c>
       <c r="J115" s="5">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>22</v>
@@ -9840,7 +9840,7 @@
         <v>125</v>
       </c>
       <c r="J116" s="2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>22</v>
@@ -9881,7 +9881,7 @@
         <v>132</v>
       </c>
       <c r="J117" s="5">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>22</v>
@@ -9922,7 +9922,7 @@
         <v>139</v>
       </c>
       <c r="J118" s="2">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>22</v>
@@ -9963,7 +9963,7 @@
         <v>146</v>
       </c>
       <c r="J119" s="5">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>22</v>
@@ -10004,7 +10004,7 @@
         <v>153</v>
       </c>
       <c r="J120" s="2">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>22</v>
@@ -10045,7 +10045,7 @@
         <v>160</v>
       </c>
       <c r="J121" s="5">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>22</v>
@@ -10127,7 +10127,7 @@
         <v>176</v>
       </c>
       <c r="J123" s="5">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="K123" s="4" t="s">
         <v>22</v>
@@ -10168,7 +10168,7 @@
         <v>183</v>
       </c>
       <c r="J124" s="2">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>22</v>
@@ -10209,7 +10209,7 @@
         <v>190</v>
       </c>
       <c r="J125" s="5">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>22</v>
@@ -10250,7 +10250,7 @@
         <v>197</v>
       </c>
       <c r="J126" s="2">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>22</v>
@@ -10291,7 +10291,7 @@
         <v>204</v>
       </c>
       <c r="J127" s="5">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>22</v>
@@ -10332,7 +10332,7 @@
         <v>211</v>
       </c>
       <c r="J128" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>22</v>
@@ -10373,7 +10373,7 @@
         <v>218</v>
       </c>
       <c r="J129" s="5">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>22</v>
@@ -10414,7 +10414,7 @@
         <v>225</v>
       </c>
       <c r="J130" s="2">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>22</v>
@@ -10455,7 +10455,7 @@
         <v>232</v>
       </c>
       <c r="J131" s="5">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>22</v>
@@ -10496,7 +10496,7 @@
         <v>241</v>
       </c>
       <c r="J132" s="2">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>22</v>
@@ -10537,7 +10537,7 @@
         <v>248</v>
       </c>
       <c r="J133" s="5">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>22</v>
@@ -10578,7 +10578,7 @@
         <v>255</v>
       </c>
       <c r="J134" s="2">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>22</v>
@@ -10619,7 +10619,7 @@
         <v>262</v>
       </c>
       <c r="J135" s="5">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>22</v>
@@ -10660,7 +10660,7 @@
         <v>269</v>
       </c>
       <c r="J136" s="2">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>22</v>
@@ -10701,7 +10701,7 @@
         <v>276</v>
       </c>
       <c r="J137" s="5">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>22</v>
@@ -10742,7 +10742,7 @@
         <v>283</v>
       </c>
       <c r="J138" s="2">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>22</v>
@@ -10783,7 +10783,7 @@
         <v>290</v>
       </c>
       <c r="J139" s="5">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>22</v>
@@ -10824,7 +10824,7 @@
         <v>297</v>
       </c>
       <c r="J140" s="2">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>22</v>
@@ -10865,7 +10865,7 @@
         <v>304</v>
       </c>
       <c r="J141" s="5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>22</v>
@@ -10906,7 +10906,7 @@
         <v>313</v>
       </c>
       <c r="J142" s="2">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>22</v>
@@ -10947,7 +10947,7 @@
         <v>320</v>
       </c>
       <c r="J143" s="5">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>22</v>
@@ -10988,7 +10988,7 @@
         <v>327</v>
       </c>
       <c r="J144" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>22</v>
@@ -11029,7 +11029,7 @@
         <v>334</v>
       </c>
       <c r="J145" s="5">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>22</v>
@@ -11070,7 +11070,7 @@
         <v>341</v>
       </c>
       <c r="J146" s="2">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>22</v>
@@ -11111,7 +11111,7 @@
         <v>348</v>
       </c>
       <c r="J147" s="5">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>22</v>
@@ -11152,7 +11152,7 @@
         <v>355</v>
       </c>
       <c r="J148" s="2">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>22</v>
@@ -11193,7 +11193,7 @@
         <v>362</v>
       </c>
       <c r="J149" s="5">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>22</v>
@@ -11234,7 +11234,7 @@
         <v>369</v>
       </c>
       <c r="J150" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>22</v>
@@ -11275,7 +11275,7 @@
         <v>376</v>
       </c>
       <c r="J151" s="5">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>22</v>
@@ -11316,7 +11316,7 @@
         <v>385</v>
       </c>
       <c r="J152" s="2">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>22</v>
@@ -11357,7 +11357,7 @@
         <v>392</v>
       </c>
       <c r="J153" s="5">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>22</v>
@@ -11398,7 +11398,7 @@
         <v>399</v>
       </c>
       <c r="J154" s="2">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>22</v>
@@ -11439,7 +11439,7 @@
         <v>406</v>
       </c>
       <c r="J155" s="5">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>22</v>
@@ -11480,7 +11480,7 @@
         <v>413</v>
       </c>
       <c r="J156" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>22</v>
@@ -11562,7 +11562,7 @@
         <v>427</v>
       </c>
       <c r="J158" s="2">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>22</v>
@@ -11603,7 +11603,7 @@
         <v>434</v>
       </c>
       <c r="J159" s="5">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>22</v>
@@ -11644,7 +11644,7 @@
         <v>441</v>
       </c>
       <c r="J160" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>22</v>
@@ -11685,7 +11685,7 @@
         <v>448</v>
       </c>
       <c r="J161" s="5">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>22</v>
@@ -11726,7 +11726,7 @@
         <v>457</v>
       </c>
       <c r="J162" s="2">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>22</v>
@@ -11767,7 +11767,7 @@
         <v>464</v>
       </c>
       <c r="J163" s="5">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>22</v>
@@ -11808,7 +11808,7 @@
         <v>471</v>
       </c>
       <c r="J164" s="2">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>22</v>
@@ -11849,7 +11849,7 @@
         <v>478</v>
       </c>
       <c r="J165" s="5">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>22</v>
@@ -11890,7 +11890,7 @@
         <v>485</v>
       </c>
       <c r="J166" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>22</v>
@@ -11931,7 +11931,7 @@
         <v>492</v>
       </c>
       <c r="J167" s="5">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>22</v>
@@ -11972,7 +11972,7 @@
         <v>499</v>
       </c>
       <c r="J168" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>22</v>
@@ -12013,7 +12013,7 @@
         <v>506</v>
       </c>
       <c r="J169" s="5">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>22</v>
@@ -12054,7 +12054,7 @@
         <v>513</v>
       </c>
       <c r="J170" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>22</v>
@@ -12095,7 +12095,7 @@
         <v>520</v>
       </c>
       <c r="J171" s="5">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>22</v>
@@ -12136,7 +12136,7 @@
         <v>529</v>
       </c>
       <c r="J172" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>22</v>
@@ -12177,7 +12177,7 @@
         <v>536</v>
       </c>
       <c r="J173" s="5">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="K173" s="4" t="s">
         <v>22</v>
@@ -12218,7 +12218,7 @@
         <v>543</v>
       </c>
       <c r="J174" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>22</v>
@@ -12259,7 +12259,7 @@
         <v>550</v>
       </c>
       <c r="J175" s="5">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>22</v>
@@ -12300,7 +12300,7 @@
         <v>557</v>
       </c>
       <c r="J176" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>22</v>
@@ -12341,7 +12341,7 @@
         <v>564</v>
       </c>
       <c r="J177" s="5">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>22</v>
@@ -12382,7 +12382,7 @@
         <v>571</v>
       </c>
       <c r="J178" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>22</v>
@@ -12423,7 +12423,7 @@
         <v>578</v>
       </c>
       <c r="J179" s="5">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>22</v>
@@ -12464,7 +12464,7 @@
         <v>585</v>
       </c>
       <c r="J180" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>22</v>
@@ -12505,7 +12505,7 @@
         <v>592</v>
       </c>
       <c r="J181" s="5">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>22</v>
@@ -12546,7 +12546,7 @@
         <v>601</v>
       </c>
       <c r="J182" s="2">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>22</v>
@@ -12587,7 +12587,7 @@
         <v>608</v>
       </c>
       <c r="J183" s="5">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>22</v>
@@ -12628,7 +12628,7 @@
         <v>615</v>
       </c>
       <c r="J184" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K184" s="4" t="s">
         <v>22</v>
@@ -12669,7 +12669,7 @@
         <v>622</v>
       </c>
       <c r="J185" s="5">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>22</v>
@@ -12710,7 +12710,7 @@
         <v>629</v>
       </c>
       <c r="J186" s="2">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>22</v>
@@ -12751,7 +12751,7 @@
         <v>636</v>
       </c>
       <c r="J187" s="5">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="K187" s="4" t="s">
         <v>22</v>
@@ -12792,7 +12792,7 @@
         <v>643</v>
       </c>
       <c r="J188" s="2">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>22</v>
@@ -12833,7 +12833,7 @@
         <v>650</v>
       </c>
       <c r="J189" s="5">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>22</v>
@@ -12874,7 +12874,7 @@
         <v>657</v>
       </c>
       <c r="J190" s="2">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>22</v>
@@ -12915,7 +12915,7 @@
         <v>664</v>
       </c>
       <c r="J191" s="5">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="K191" s="4" t="s">
         <v>22</v>
@@ -12956,7 +12956,7 @@
         <v>673</v>
       </c>
       <c r="J192" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="K192" s="4" t="s">
         <v>22</v>
@@ -12997,7 +12997,7 @@
         <v>680</v>
       </c>
       <c r="J193" s="5">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K193" s="4" t="s">
         <v>22</v>
@@ -13038,7 +13038,7 @@
         <v>687</v>
       </c>
       <c r="J194" s="2">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="K194" s="4" t="s">
         <v>22</v>
@@ -13079,7 +13079,7 @@
         <v>694</v>
       </c>
       <c r="J195" s="5">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K195" s="4" t="s">
         <v>22</v>
@@ -13120,7 +13120,7 @@
         <v>701</v>
       </c>
       <c r="J196" s="2">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K196" s="4" t="s">
         <v>22</v>
@@ -13161,7 +13161,7 @@
         <v>708</v>
       </c>
       <c r="J197" s="5">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K197" s="4" t="s">
         <v>22</v>
@@ -13202,7 +13202,7 @@
         <v>715</v>
       </c>
       <c r="J198" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K198" s="4" t="s">
         <v>22</v>
@@ -13243,7 +13243,7 @@
         <v>722</v>
       </c>
       <c r="J199" s="5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K199" s="4" t="s">
         <v>22</v>
@@ -13284,7 +13284,7 @@
         <v>729</v>
       </c>
       <c r="J200" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K200" s="4" t="s">
         <v>22</v>
@@ -13325,7 +13325,7 @@
         <v>736</v>
       </c>
       <c r="J201" s="5">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K201" s="4" t="s">
         <v>22</v>
@@ -13366,7 +13366,7 @@
         <v>21</v>
       </c>
       <c r="J202" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="K202" s="4" t="s">
         <v>22</v>
@@ -13407,7 +13407,7 @@
         <v>30</v>
       </c>
       <c r="J203" s="5">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="K203" s="4" t="s">
         <v>22</v>
@@ -13448,7 +13448,7 @@
         <v>38</v>
       </c>
       <c r="J204" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="K204" s="4" t="s">
         <v>22</v>
@@ -13489,7 +13489,7 @@
         <v>45</v>
       </c>
       <c r="J205" s="5">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="K205" s="4" t="s">
         <v>22</v>
@@ -13530,7 +13530,7 @@
         <v>52</v>
       </c>
       <c r="J206" s="2">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="K206" s="4" t="s">
         <v>22</v>
@@ -13571,7 +13571,7 @@
         <v>60</v>
       </c>
       <c r="J207" s="5">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="K207" s="4" t="s">
         <v>22</v>
@@ -13612,7 +13612,7 @@
         <v>67</v>
       </c>
       <c r="J208" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="K208" s="4" t="s">
         <v>22</v>
@@ -13653,7 +13653,7 @@
         <v>74</v>
       </c>
       <c r="J209" s="5">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="K209" s="4" t="s">
         <v>22</v>
@@ -13694,7 +13694,7 @@
         <v>81</v>
       </c>
       <c r="J210" s="2">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="K210" s="4" t="s">
         <v>22</v>
@@ -13735,7 +13735,7 @@
         <v>88</v>
       </c>
       <c r="J211" s="5">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="K211" s="4" t="s">
         <v>22</v>
@@ -13776,7 +13776,7 @@
         <v>97</v>
       </c>
       <c r="J212" s="2">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="K212" s="4" t="s">
         <v>22</v>
@@ -13817,7 +13817,7 @@
         <v>104</v>
       </c>
       <c r="J213" s="5">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="K213" s="4" t="s">
         <v>22</v>
@@ -13858,7 +13858,7 @@
         <v>111</v>
       </c>
       <c r="J214" s="2">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="K214" s="4" t="s">
         <v>22</v>
@@ -13899,7 +13899,7 @@
         <v>118</v>
       </c>
       <c r="J215" s="5">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="K215" s="4" t="s">
         <v>22</v>
@@ -13940,7 +13940,7 @@
         <v>125</v>
       </c>
       <c r="J216" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K216" s="4" t="s">
         <v>22</v>
@@ -13981,7 +13981,7 @@
         <v>132</v>
       </c>
       <c r="J217" s="5">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="K217" s="4" t="s">
         <v>22</v>
@@ -14022,7 +14022,7 @@
         <v>139</v>
       </c>
       <c r="J218" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K218" s="4" t="s">
         <v>22</v>
@@ -14063,7 +14063,7 @@
         <v>146</v>
       </c>
       <c r="J219" s="5">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="K219" s="4" t="s">
         <v>22</v>
@@ -14104,7 +14104,7 @@
         <v>153</v>
       </c>
       <c r="J220" s="2">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="K220" s="4" t="s">
         <v>22</v>
@@ -14145,7 +14145,7 @@
         <v>160</v>
       </c>
       <c r="J221" s="5">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="K221" s="4" t="s">
         <v>22</v>
@@ -14186,7 +14186,7 @@
         <v>169</v>
       </c>
       <c r="J222" s="2">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="K222" s="4" t="s">
         <v>22</v>
@@ -14227,7 +14227,7 @@
         <v>176</v>
       </c>
       <c r="J223" s="5">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="K223" s="4" t="s">
         <v>22</v>
@@ -14268,7 +14268,7 @@
         <v>183</v>
       </c>
       <c r="J224" s="2">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>22</v>
@@ -14309,7 +14309,7 @@
         <v>190</v>
       </c>
       <c r="J225" s="5">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>22</v>
@@ -14350,7 +14350,7 @@
         <v>197</v>
       </c>
       <c r="J226" s="2">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="K226" s="4" t="s">
         <v>22</v>
@@ -14391,7 +14391,7 @@
         <v>204</v>
       </c>
       <c r="J227" s="5">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="K227" s="4" t="s">
         <v>22</v>
@@ -14432,7 +14432,7 @@
         <v>211</v>
       </c>
       <c r="J228" s="2">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="K228" s="4" t="s">
         <v>22</v>
@@ -14473,7 +14473,7 @@
         <v>218</v>
       </c>
       <c r="J229" s="5">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K229" s="4" t="s">
         <v>22</v>
@@ -14514,7 +14514,7 @@
         <v>225</v>
       </c>
       <c r="J230" s="2">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="K230" s="4" t="s">
         <v>22</v>
@@ -14555,7 +14555,7 @@
         <v>232</v>
       </c>
       <c r="J231" s="5">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="K231" s="4" t="s">
         <v>22</v>
@@ -14596,7 +14596,7 @@
         <v>241</v>
       </c>
       <c r="J232" s="2">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="K232" s="4" t="s">
         <v>22</v>
@@ -14637,7 +14637,7 @@
         <v>248</v>
       </c>
       <c r="J233" s="5">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="K233" s="4" t="s">
         <v>22</v>
@@ -14678,7 +14678,7 @@
         <v>255</v>
       </c>
       <c r="J234" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K234" s="4" t="s">
         <v>22</v>
@@ -14719,7 +14719,7 @@
         <v>262</v>
       </c>
       <c r="J235" s="5">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="K235" s="4" t="s">
         <v>22</v>
@@ -14760,7 +14760,7 @@
         <v>269</v>
       </c>
       <c r="J236" s="2">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="K236" s="4" t="s">
         <v>22</v>
@@ -14801,7 +14801,7 @@
         <v>276</v>
       </c>
       <c r="J237" s="5">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="K237" s="4" t="s">
         <v>22</v>
@@ -14842,7 +14842,7 @@
         <v>283</v>
       </c>
       <c r="J238" s="2">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="K238" s="4" t="s">
         <v>22</v>
@@ -14883,7 +14883,7 @@
         <v>290</v>
       </c>
       <c r="J239" s="5">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="K239" s="4" t="s">
         <v>22</v>
@@ -14924,7 +14924,7 @@
         <v>297</v>
       </c>
       <c r="J240" s="2">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="K240" s="4" t="s">
         <v>22</v>
@@ -14965,7 +14965,7 @@
         <v>304</v>
       </c>
       <c r="J241" s="5">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K241" s="4" t="s">
         <v>22</v>
@@ -15006,7 +15006,7 @@
         <v>313</v>
       </c>
       <c r="J242" s="2">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>22</v>
@@ -15047,7 +15047,7 @@
         <v>320</v>
       </c>
       <c r="J243" s="5">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>22</v>
@@ -15088,7 +15088,7 @@
         <v>327</v>
       </c>
       <c r="J244" s="2">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="K244" s="4" t="s">
         <v>22</v>
@@ -15129,7 +15129,7 @@
         <v>334</v>
       </c>
       <c r="J245" s="5">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="K245" s="4" t="s">
         <v>22</v>
@@ -15170,7 +15170,7 @@
         <v>341</v>
       </c>
       <c r="J246" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K246" s="4" t="s">
         <v>22</v>
@@ -15211,7 +15211,7 @@
         <v>348</v>
       </c>
       <c r="J247" s="5">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K247" s="4" t="s">
         <v>22</v>
@@ -15252,7 +15252,7 @@
         <v>355</v>
       </c>
       <c r="J248" s="2">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="K248" s="4" t="s">
         <v>22</v>
@@ -15293,7 +15293,7 @@
         <v>362</v>
       </c>
       <c r="J249" s="5">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="K249" s="4" t="s">
         <v>22</v>
@@ -15334,7 +15334,7 @@
         <v>369</v>
       </c>
       <c r="J250" s="2">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>22</v>
@@ -15375,7 +15375,7 @@
         <v>376</v>
       </c>
       <c r="J251" s="5">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="K251" s="4" t="s">
         <v>22</v>
@@ -15416,7 +15416,7 @@
         <v>385</v>
       </c>
       <c r="J252" s="2">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="K252" s="4" t="s">
         <v>22</v>
@@ -15457,7 +15457,7 @@
         <v>392</v>
       </c>
       <c r="J253" s="5">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="K253" s="4" t="s">
         <v>22</v>
@@ -15498,7 +15498,7 @@
         <v>399</v>
       </c>
       <c r="J254" s="2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K254" s="4" t="s">
         <v>22</v>
@@ -15539,7 +15539,7 @@
         <v>406</v>
       </c>
       <c r="J255" s="5">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="K255" s="4" t="s">
         <v>22</v>
@@ -15580,7 +15580,7 @@
         <v>413</v>
       </c>
       <c r="J256" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K256" s="4" t="s">
         <v>22</v>
@@ -15621,7 +15621,7 @@
         <v>420</v>
       </c>
       <c r="J257" s="5">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="K257" s="4" t="s">
         <v>22</v>
@@ -15662,7 +15662,7 @@
         <v>427</v>
       </c>
       <c r="J258" s="2">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="K258" s="4" t="s">
         <v>22</v>
@@ -15703,7 +15703,7 @@
         <v>434</v>
       </c>
       <c r="J259" s="5">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K259" s="4" t="s">
         <v>22</v>
@@ -15744,7 +15744,7 @@
         <v>441</v>
       </c>
       <c r="J260" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="K260" s="4" t="s">
         <v>22</v>
@@ -15785,7 +15785,7 @@
         <v>448</v>
       </c>
       <c r="J261" s="5">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="K261" s="4" t="s">
         <v>22</v>
@@ -15826,7 +15826,7 @@
         <v>457</v>
       </c>
       <c r="J262" s="2">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="K262" s="4" t="s">
         <v>22</v>
@@ -15867,7 +15867,7 @@
         <v>464</v>
       </c>
       <c r="J263" s="5">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>22</v>
@@ -15908,7 +15908,7 @@
         <v>471</v>
       </c>
       <c r="J264" s="2">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="K264" s="4" t="s">
         <v>22</v>
@@ -15990,7 +15990,7 @@
         <v>485</v>
       </c>
       <c r="J266" s="2">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="K266" s="4" t="s">
         <v>22</v>
@@ -16031,7 +16031,7 @@
         <v>492</v>
       </c>
       <c r="J267" s="5">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="K267" s="4" t="s">
         <v>22</v>
@@ -16072,7 +16072,7 @@
         <v>499</v>
       </c>
       <c r="J268" s="2">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="K268" s="4" t="s">
         <v>22</v>
@@ -16113,7 +16113,7 @@
         <v>506</v>
       </c>
       <c r="J269" s="5">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="K269" s="4" t="s">
         <v>22</v>
@@ -16154,7 +16154,7 @@
         <v>513</v>
       </c>
       <c r="J270" s="2">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="K270" s="4" t="s">
         <v>22</v>
@@ -16195,7 +16195,7 @@
         <v>520</v>
       </c>
       <c r="J271" s="5">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K271" s="4" t="s">
         <v>22</v>
@@ -16236,7 +16236,7 @@
         <v>529</v>
       </c>
       <c r="J272" s="2">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K272" s="4" t="s">
         <v>22</v>
@@ -16277,7 +16277,7 @@
         <v>536</v>
       </c>
       <c r="J273" s="5">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="K273" s="4" t="s">
         <v>22</v>
@@ -16318,7 +16318,7 @@
         <v>543</v>
       </c>
       <c r="J274" s="2">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="K274" s="4" t="s">
         <v>22</v>
@@ -16359,7 +16359,7 @@
         <v>550</v>
       </c>
       <c r="J275" s="5">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="K275" s="4" t="s">
         <v>22</v>
@@ -16400,7 +16400,7 @@
         <v>557</v>
       </c>
       <c r="J276" s="2">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="K276" s="4" t="s">
         <v>22</v>
@@ -16441,7 +16441,7 @@
         <v>564</v>
       </c>
       <c r="J277" s="5">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="K277" s="4" t="s">
         <v>22</v>
@@ -16482,7 +16482,7 @@
         <v>571</v>
       </c>
       <c r="J278" s="2">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="K278" s="4" t="s">
         <v>22</v>
@@ -16523,7 +16523,7 @@
         <v>578</v>
       </c>
       <c r="J279" s="5">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="K279" s="4" t="s">
         <v>22</v>
@@ -16564,7 +16564,7 @@
         <v>585</v>
       </c>
       <c r="J280" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K280" s="4" t="s">
         <v>22</v>
@@ -16605,7 +16605,7 @@
         <v>592</v>
       </c>
       <c r="J281" s="5">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="K281" s="4" t="s">
         <v>22</v>
@@ -16646,7 +16646,7 @@
         <v>601</v>
       </c>
       <c r="J282" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="K282" s="4" t="s">
         <v>22</v>
@@ -16687,7 +16687,7 @@
         <v>608</v>
       </c>
       <c r="J283" s="5">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="K283" s="4" t="s">
         <v>22</v>
@@ -16728,7 +16728,7 @@
         <v>615</v>
       </c>
       <c r="J284" s="2">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="K284" s="4" t="s">
         <v>22</v>
@@ -16769,7 +16769,7 @@
         <v>622</v>
       </c>
       <c r="J285" s="5">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="K285" s="4" t="s">
         <v>22</v>
@@ -16810,7 +16810,7 @@
         <v>629</v>
       </c>
       <c r="J286" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="K286" s="4" t="s">
         <v>22</v>
@@ -16851,7 +16851,7 @@
         <v>636</v>
       </c>
       <c r="J287" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K287" s="4" t="s">
         <v>22</v>
@@ -16892,7 +16892,7 @@
         <v>643</v>
       </c>
       <c r="J288" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="K288" s="4" t="s">
         <v>22</v>
@@ -16933,7 +16933,7 @@
         <v>650</v>
       </c>
       <c r="J289" s="5">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="K289" s="4" t="s">
         <v>22</v>
@@ -16974,7 +16974,7 @@
         <v>657</v>
       </c>
       <c r="J290" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="K290" s="4" t="s">
         <v>22</v>
@@ -17015,7 +17015,7 @@
         <v>664</v>
       </c>
       <c r="J291" s="5">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K291" s="4" t="s">
         <v>22</v>
@@ -17056,7 +17056,7 @@
         <v>673</v>
       </c>
       <c r="J292" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K292" s="4" t="s">
         <v>22</v>
@@ -17097,7 +17097,7 @@
         <v>680</v>
       </c>
       <c r="J293" s="5">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="K293" s="4" t="s">
         <v>22</v>
@@ -17138,7 +17138,7 @@
         <v>687</v>
       </c>
       <c r="J294" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="K294" s="4" t="s">
         <v>22</v>
@@ -17179,7 +17179,7 @@
         <v>694</v>
       </c>
       <c r="J295" s="5">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="K295" s="4" t="s">
         <v>22</v>
@@ -17220,7 +17220,7 @@
         <v>701</v>
       </c>
       <c r="J296" s="2">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="K296" s="4" t="s">
         <v>22</v>
@@ -17261,7 +17261,7 @@
         <v>708</v>
       </c>
       <c r="J297" s="5">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="K297" s="4" t="s">
         <v>22</v>
@@ -17302,7 +17302,7 @@
         <v>715</v>
       </c>
       <c r="J298" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="K298" s="4" t="s">
         <v>22</v>
@@ -17343,7 +17343,7 @@
         <v>722</v>
       </c>
       <c r="J299" s="5">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="K299" s="4" t="s">
         <v>22</v>
@@ -17384,7 +17384,7 @@
         <v>729</v>
       </c>
       <c r="J300" s="2">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="K300" s="4" t="s">
         <v>22</v>
@@ -17425,7 +17425,7 @@
         <v>736</v>
       </c>
       <c r="J301" s="5">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="K301" s="4" t="s">
         <v>22</v>
